--- a/downloads/Verizon_Vodafone_MA_Analysis.xlsx
+++ b/downloads/Verizon_Vodafone_MA_Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/akulveauli/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{016A93D1-5885-9240-9364-9C6A862AC9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4A5FF0-EF66-2145-A280-9B84D7578B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{0A50C6A4-022B-8E46-B6B9-7BD663B01CE9}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16940" xr2:uid="{0A50C6A4-022B-8E46-B6B9-7BD663B01CE9}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover Page" sheetId="2" r:id="rId1"/>
@@ -30,9 +30,9 @@
     <sheet name="Assumptions (3) Old" sheetId="26" state="hidden" r:id="rId15"/>
     <sheet name="EPS Accretion-Dilution (3) old" sheetId="27" state="hidden" r:id="rId16"/>
     <sheet name="Deal Structure (3) Old" sheetId="28" state="hidden" r:id="rId17"/>
-    <sheet name="Assumptions (3)" sheetId="29" r:id="rId18"/>
-    <sheet name="EPS Accretion-Dilution (3)" sheetId="30" r:id="rId19"/>
-    <sheet name="Deal Structure (3)" sheetId="31" r:id="rId20"/>
+    <sheet name="Assumptions (VF)" sheetId="29" r:id="rId18"/>
+    <sheet name="EPS Accretion-Dilution (VF)" sheetId="30" r:id="rId19"/>
+    <sheet name="Deal Structure (VF)" sheetId="31" r:id="rId20"/>
     <sheet name="ROIC VS WACC -&gt;" sheetId="34" r:id="rId21"/>
     <sheet name="ROIC vs WACC" sheetId="36" r:id="rId22"/>
     <sheet name="Deal Structure &amp; Capital Impact" sheetId="37" r:id="rId23"/>
@@ -146,7 +146,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -155,12 +155,21 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Based on broader 10 year normalized calculation ETR works out to be 23.19%</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Based on broader 10 year normalized calculation ETR works out to be 23.19%</t>
         </r>
       </text>
     </comment>
@@ -305,7 +314,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="447">
   <si>
     <t>VERIZON / VODAFONE  – M&amp;A Deal Analysis</t>
   </si>
@@ -1596,9 +1605,6 @@
   </si>
   <si>
     <t>Cash</t>
-  </si>
-  <si>
-    <t>~0%</t>
   </si>
   <si>
     <t>Transaction costs &amp; fees</t>
@@ -1656,7 +1662,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="13">
+  <numFmts count="14">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="\$#,##0.0;&quot;($&quot;#,##0.0\);\-"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
@@ -1668,8 +1674,9 @@
     <numFmt numFmtId="171" formatCode="0.0%;\(0.0%\);&quot;-&quot;"/>
     <numFmt numFmtId="172" formatCode="\$#,##0.0;\(\$#,##0.0\);&quot;-&quot;"/>
     <numFmt numFmtId="173" formatCode="#,##0.0;\(#,##0.0\);&quot;-&quot;"/>
-    <numFmt numFmtId="178" formatCode="#,##0;\(#,##0\);\-"/>
-    <numFmt numFmtId="179" formatCode="0.00%;\(0.00%\);\-"/>
+    <numFmt numFmtId="174" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="175" formatCode="0.00%;\(0.00%\);\-"/>
+    <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
   <fonts count="50" x14ac:knownFonts="1">
     <font>
@@ -2192,7 +2199,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -2336,6 +2343,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2343,7 +2365,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="243">
+  <cellXfs count="246">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2663,10 +2685,261 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="9" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="9" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="9" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="14" borderId="0" xfId="3" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="15" fillId="16" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="13" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="15" fillId="17" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="13" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="15" fillId="16" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="15" fillId="17" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="15" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="15" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="12" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="12" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="11" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="12" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="21" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="22" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="8" fillId="21" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="8" fillId="22" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="11" fillId="24" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="8" fillId="25" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="9" fillId="26" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="26" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="11" fillId="24" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="9" fillId="26" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="26" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="29" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="19" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="18" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="20" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="20" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="6" fillId="20" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="18" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="19" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="24" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="42" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="11" fillId="24" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2695,298 +2968,50 @@
     <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="11" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="11" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="9" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="9" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="9" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="9" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="14" borderId="0" xfId="3" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="15" fillId="16" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="13" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="15" fillId="17" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="13" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="15" fillId="16" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="15" fillId="17" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="15" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="15" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="12" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="12" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="11" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="12" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="12" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="19" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="43" fillId="18" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="19" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="31" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="30" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="28" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="20" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="21" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="22" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="21" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="22" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="24" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="25" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="26" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="26" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="24" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="26" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="26" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="28" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="29" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="30" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="31" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="19" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="18" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="47" fillId="31" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="20" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="20" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="20" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="18" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="19" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="24" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2997,6 +3022,16 @@
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="24">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3034,6 +3069,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3119,11 +3164,41 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3149,21 +3224,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3187,56 +3262,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -3254,10 +3279,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3585,40 +3606,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="217" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
-      <c r="M1" s="131"/>
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="217"/>
+      <c r="J1" s="217"/>
+      <c r="K1" s="217"/>
+      <c r="L1" s="217"/>
+      <c r="M1" s="217"/>
     </row>
     <row r="2" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="132" t="s">
+      <c r="A2" s="218" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B2" s="218"/>
+      <c r="C2" s="218"/>
+      <c r="D2" s="218"/>
+      <c r="E2" s="218"/>
+      <c r="F2" s="218"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="218"/>
+      <c r="I2" s="218"/>
+      <c r="J2" s="218"/>
+      <c r="K2" s="218"/>
+      <c r="L2" s="218"/>
+      <c r="M2" s="218"/>
+    </row>
+    <row r="3" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="100"/>
       <c r="B3" s="100"/>
       <c r="C3" s="100"/>
@@ -3627,11 +3648,11 @@
       <c r="F3" s="100"/>
       <c r="G3" s="100"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="213" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3713,26 +3734,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="223" t="s">
         <v>244</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
+      <c r="B1" s="224"/>
+      <c r="C1" s="224"/>
+      <c r="D1" s="224"/>
+      <c r="E1" s="224"/>
+      <c r="F1" s="224"/>
+      <c r="G1" s="224"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="225" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
-      <c r="G2" s="137"/>
+      <c r="B2" s="224"/>
+      <c r="C2" s="224"/>
+      <c r="D2" s="224"/>
+      <c r="E2" s="224"/>
+      <c r="F2" s="224"/>
+      <c r="G2" s="224"/>
     </row>
     <row r="3" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4125,28 +4146,28 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="142" t="s">
+      <c r="A29" s="229" t="s">
         <v>264</v>
       </c>
-      <c r="B29" s="137"/>
-      <c r="C29" s="137"/>
+      <c r="B29" s="224"/>
+      <c r="C29" s="224"/>
     </row>
     <row r="30" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="137"/>
-      <c r="B30" s="137"/>
-      <c r="C30" s="137"/>
+      <c r="A30" s="224"/>
+      <c r="B30" s="224"/>
+      <c r="C30" s="224"/>
     </row>
     <row r="31" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="139" t="s">
+      <c r="A32" s="226" t="s">
         <v>183</v>
       </c>
-      <c r="B32" s="137"/>
-      <c r="C32" s="137"/>
-      <c r="D32" s="137"/>
-      <c r="E32" s="137"/>
-      <c r="F32" s="137"/>
-      <c r="G32" s="137"/>
+      <c r="B32" s="224"/>
+      <c r="C32" s="224"/>
+      <c r="D32" s="224"/>
+      <c r="E32" s="224"/>
+      <c r="F32" s="224"/>
+      <c r="G32" s="224"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4172,22 +4193,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="223" t="s">
         <v>265</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
+      <c r="B1" s="224"/>
+      <c r="C1" s="224"/>
+      <c r="D1" s="224"/>
+      <c r="E1" s="224"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="225" t="s">
         <v>266</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
+      <c r="B2" s="224"/>
+      <c r="C2" s="224"/>
+      <c r="D2" s="224"/>
+      <c r="E2" s="224"/>
     </row>
     <row r="3" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4527,46 +4548,46 @@
     </row>
     <row r="33" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="139" t="s">
+      <c r="A34" s="226" t="s">
         <v>267</v>
       </c>
-      <c r="B34" s="137"/>
-      <c r="C34" s="137"/>
-      <c r="D34" s="137"/>
-      <c r="E34" s="137"/>
+      <c r="B34" s="224"/>
+      <c r="C34" s="224"/>
+      <c r="D34" s="224"/>
+      <c r="E34" s="224"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="141" t="s">
+      <c r="A35" s="228" t="s">
         <v>211</v>
       </c>
-      <c r="B35" s="137"/>
-      <c r="C35" s="137"/>
-      <c r="D35" s="137"/>
-      <c r="E35" s="137"/>
-      <c r="F35" s="137"/>
-      <c r="G35" s="137"/>
+      <c r="B35" s="224"/>
+      <c r="C35" s="224"/>
+      <c r="D35" s="224"/>
+      <c r="E35" s="224"/>
+      <c r="F35" s="224"/>
+      <c r="G35" s="224"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="138" t="s">
+      <c r="A36" s="225" t="s">
         <v>268</v>
       </c>
-      <c r="B36" s="137"/>
-      <c r="C36" s="137"/>
-      <c r="D36" s="137"/>
-      <c r="E36" s="137"/>
-      <c r="F36" s="137"/>
-      <c r="G36" s="137"/>
+      <c r="B36" s="224"/>
+      <c r="C36" s="224"/>
+      <c r="D36" s="224"/>
+      <c r="E36" s="224"/>
+      <c r="F36" s="224"/>
+      <c r="G36" s="224"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="140" t="s">
+      <c r="A38" s="227" t="s">
         <v>269</v>
       </c>
-      <c r="B38" s="137"/>
-      <c r="C38" s="137"/>
-      <c r="D38" s="137"/>
-      <c r="E38" s="137"/>
-      <c r="F38" s="137"/>
-      <c r="G38" s="137"/>
+      <c r="B38" s="224"/>
+      <c r="C38" s="224"/>
+      <c r="D38" s="224"/>
+      <c r="E38" s="224"/>
+      <c r="F38" s="224"/>
+      <c r="G38" s="224"/>
     </row>
     <row r="39" spans="1:7" ht="26" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
@@ -4753,15 +4774,15 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="140" t="s">
+      <c r="A48" s="227" t="s">
         <v>221</v>
       </c>
-      <c r="B48" s="137"/>
-      <c r="C48" s="137"/>
-      <c r="D48" s="137"/>
-      <c r="E48" s="137"/>
-      <c r="F48" s="137"/>
-      <c r="G48" s="137"/>
+      <c r="B48" s="224"/>
+      <c r="C48" s="224"/>
+      <c r="D48" s="224"/>
+      <c r="E48" s="224"/>
+      <c r="F48" s="224"/>
+      <c r="G48" s="224"/>
     </row>
     <row r="49" spans="1:7" ht="26" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -4948,15 +4969,15 @@
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57" s="139" t="s">
+      <c r="A57" s="226" t="s">
         <v>277</v>
       </c>
-      <c r="B57" s="137"/>
-      <c r="C57" s="137"/>
-      <c r="D57" s="137"/>
-      <c r="E57" s="137"/>
-      <c r="F57" s="137"/>
-      <c r="G57" s="137"/>
+      <c r="B57" s="224"/>
+      <c r="C57" s="224"/>
+      <c r="D57" s="224"/>
+      <c r="E57" s="224"/>
+      <c r="F57" s="224"/>
+      <c r="G57" s="224"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4987,20 +5008,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="228" t="s">
         <v>222</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
+      <c r="B1" s="224"/>
+      <c r="C1" s="224"/>
+      <c r="D1" s="224"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="225" t="s">
         <v>223</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="B2" s="224"/>
+      <c r="C2" s="224"/>
+      <c r="D2" s="224"/>
     </row>
     <row r="3" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5157,87 +5178,87 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="219" t="s">
         <v>283</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
-      <c r="L1" s="143"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="143"/>
-      <c r="O1" s="143"/>
-      <c r="P1" s="143"/>
-      <c r="Q1" s="143"/>
-      <c r="R1" s="143"/>
-      <c r="S1" s="143"/>
-      <c r="T1" s="143"/>
-      <c r="U1" s="143"/>
-      <c r="V1" s="143"/>
-      <c r="W1" s="143"/>
-      <c r="X1" s="143"/>
-      <c r="Y1" s="143"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="219"/>
+      <c r="K1" s="219"/>
+      <c r="L1" s="219"/>
+      <c r="M1" s="219"/>
+      <c r="N1" s="219"/>
+      <c r="O1" s="219"/>
+      <c r="P1" s="219"/>
+      <c r="Q1" s="219"/>
+      <c r="R1" s="219"/>
+      <c r="S1" s="219"/>
+      <c r="T1" s="219"/>
+      <c r="U1" s="219"/>
+      <c r="V1" s="219"/>
+      <c r="W1" s="219"/>
+      <c r="X1" s="219"/>
+      <c r="Y1" s="219"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="143"/>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="143"/>
-      <c r="K2" s="143"/>
-      <c r="L2" s="143"/>
-      <c r="M2" s="143"/>
-      <c r="N2" s="143"/>
-      <c r="O2" s="143"/>
-      <c r="P2" s="143"/>
-      <c r="Q2" s="143"/>
-      <c r="R2" s="143"/>
-      <c r="S2" s="143"/>
-      <c r="T2" s="143"/>
-      <c r="U2" s="143"/>
-      <c r="V2" s="143"/>
-      <c r="W2" s="143"/>
-      <c r="X2" s="143"/>
-      <c r="Y2" s="143"/>
+      <c r="A2" s="219"/>
+      <c r="B2" s="219"/>
+      <c r="C2" s="219"/>
+      <c r="D2" s="219"/>
+      <c r="E2" s="219"/>
+      <c r="F2" s="219"/>
+      <c r="G2" s="219"/>
+      <c r="H2" s="219"/>
+      <c r="I2" s="219"/>
+      <c r="J2" s="219"/>
+      <c r="K2" s="219"/>
+      <c r="L2" s="219"/>
+      <c r="M2" s="219"/>
+      <c r="N2" s="219"/>
+      <c r="O2" s="219"/>
+      <c r="P2" s="219"/>
+      <c r="Q2" s="219"/>
+      <c r="R2" s="219"/>
+      <c r="S2" s="219"/>
+      <c r="T2" s="219"/>
+      <c r="U2" s="219"/>
+      <c r="V2" s="219"/>
+      <c r="W2" s="219"/>
+      <c r="X2" s="219"/>
+      <c r="Y2" s="219"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="143"/>
-      <c r="B3" s="143"/>
-      <c r="C3" s="143"/>
-      <c r="D3" s="143"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="143"/>
-      <c r="G3" s="143"/>
-      <c r="H3" s="143"/>
-      <c r="I3" s="143"/>
-      <c r="J3" s="143"/>
-      <c r="K3" s="143"/>
-      <c r="L3" s="143"/>
-      <c r="M3" s="143"/>
-      <c r="N3" s="143"/>
-      <c r="O3" s="143"/>
-      <c r="P3" s="143"/>
-      <c r="Q3" s="143"/>
-      <c r="R3" s="143"/>
-      <c r="S3" s="143"/>
-      <c r="T3" s="143"/>
-      <c r="U3" s="143"/>
-      <c r="V3" s="143"/>
-      <c r="W3" s="143"/>
-      <c r="X3" s="143"/>
-      <c r="Y3" s="143"/>
+      <c r="A3" s="219"/>
+      <c r="B3" s="219"/>
+      <c r="C3" s="219"/>
+      <c r="D3" s="219"/>
+      <c r="E3" s="219"/>
+      <c r="F3" s="219"/>
+      <c r="G3" s="219"/>
+      <c r="H3" s="219"/>
+      <c r="I3" s="219"/>
+      <c r="J3" s="219"/>
+      <c r="K3" s="219"/>
+      <c r="L3" s="219"/>
+      <c r="M3" s="219"/>
+      <c r="N3" s="219"/>
+      <c r="O3" s="219"/>
+      <c r="P3" s="219"/>
+      <c r="Q3" s="219"/>
+      <c r="R3" s="219"/>
+      <c r="S3" s="219"/>
+      <c r="T3" s="219"/>
+      <c r="U3" s="219"/>
+      <c r="V3" s="219"/>
+      <c r="W3" s="219"/>
+      <c r="X3" s="219"/>
+      <c r="Y3" s="219"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5263,26 +5284,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="223" t="s">
         <v>244</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
+      <c r="B1" s="224"/>
+      <c r="C1" s="224"/>
+      <c r="D1" s="224"/>
+      <c r="E1" s="224"/>
+      <c r="F1" s="224"/>
+      <c r="G1" s="224"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="225" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
-      <c r="G2" s="137"/>
+      <c r="B2" s="224"/>
+      <c r="C2" s="224"/>
+      <c r="D2" s="224"/>
+      <c r="E2" s="224"/>
+      <c r="F2" s="224"/>
+      <c r="G2" s="224"/>
     </row>
     <row r="3" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5675,28 +5696,28 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="142" t="s">
+      <c r="A29" s="229" t="s">
         <v>285</v>
       </c>
-      <c r="B29" s="137"/>
-      <c r="C29" s="137"/>
+      <c r="B29" s="224"/>
+      <c r="C29" s="224"/>
     </row>
     <row r="30" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="137"/>
-      <c r="B30" s="137"/>
-      <c r="C30" s="137"/>
+      <c r="A30" s="224"/>
+      <c r="B30" s="224"/>
+      <c r="C30" s="224"/>
     </row>
     <row r="31" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="139" t="s">
+      <c r="A32" s="226" t="s">
         <v>183</v>
       </c>
-      <c r="B32" s="137"/>
-      <c r="C32" s="137"/>
-      <c r="D32" s="137"/>
-      <c r="E32" s="137"/>
-      <c r="F32" s="137"/>
-      <c r="G32" s="137"/>
+      <c r="B32" s="224"/>
+      <c r="C32" s="224"/>
+      <c r="D32" s="224"/>
+      <c r="E32" s="224"/>
+      <c r="F32" s="224"/>
+      <c r="G32" s="224"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5722,22 +5743,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="223" t="s">
         <v>286</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
+      <c r="B1" s="224"/>
+      <c r="C1" s="224"/>
+      <c r="D1" s="224"/>
+      <c r="E1" s="224"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="225" t="s">
         <v>287</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
+      <c r="B2" s="224"/>
+      <c r="C2" s="224"/>
+      <c r="D2" s="224"/>
+      <c r="E2" s="224"/>
     </row>
     <row r="3" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6077,46 +6098,46 @@
     </row>
     <row r="33" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="139" t="s">
+      <c r="A34" s="226" t="s">
         <v>267</v>
       </c>
-      <c r="B34" s="137"/>
-      <c r="C34" s="137"/>
-      <c r="D34" s="137"/>
-      <c r="E34" s="137"/>
+      <c r="B34" s="224"/>
+      <c r="C34" s="224"/>
+      <c r="D34" s="224"/>
+      <c r="E34" s="224"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="141" t="s">
+      <c r="A35" s="228" t="s">
         <v>211</v>
       </c>
-      <c r="B35" s="137"/>
-      <c r="C35" s="137"/>
-      <c r="D35" s="137"/>
-      <c r="E35" s="137"/>
-      <c r="F35" s="137"/>
-      <c r="G35" s="137"/>
+      <c r="B35" s="224"/>
+      <c r="C35" s="224"/>
+      <c r="D35" s="224"/>
+      <c r="E35" s="224"/>
+      <c r="F35" s="224"/>
+      <c r="G35" s="224"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="138" t="s">
+      <c r="A36" s="225" t="s">
         <v>288</v>
       </c>
-      <c r="B36" s="137"/>
-      <c r="C36" s="137"/>
-      <c r="D36" s="137"/>
-      <c r="E36" s="137"/>
-      <c r="F36" s="137"/>
-      <c r="G36" s="137"/>
+      <c r="B36" s="224"/>
+      <c r="C36" s="224"/>
+      <c r="D36" s="224"/>
+      <c r="E36" s="224"/>
+      <c r="F36" s="224"/>
+      <c r="G36" s="224"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="140" t="s">
+      <c r="A38" s="227" t="s">
         <v>269</v>
       </c>
-      <c r="B38" s="137"/>
-      <c r="C38" s="137"/>
-      <c r="D38" s="137"/>
-      <c r="E38" s="137"/>
-      <c r="F38" s="137"/>
-      <c r="G38" s="137"/>
+      <c r="B38" s="224"/>
+      <c r="C38" s="224"/>
+      <c r="D38" s="224"/>
+      <c r="E38" s="224"/>
+      <c r="F38" s="224"/>
+      <c r="G38" s="224"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
@@ -6303,15 +6324,15 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="140" t="s">
+      <c r="A48" s="227" t="s">
         <v>221</v>
       </c>
-      <c r="B48" s="137"/>
-      <c r="C48" s="137"/>
-      <c r="D48" s="137"/>
-      <c r="E48" s="137"/>
-      <c r="F48" s="137"/>
-      <c r="G48" s="137"/>
+      <c r="B48" s="224"/>
+      <c r="C48" s="224"/>
+      <c r="D48" s="224"/>
+      <c r="E48" s="224"/>
+      <c r="F48" s="224"/>
+      <c r="G48" s="224"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -6498,15 +6519,15 @@
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57" s="139" t="s">
+      <c r="A57" s="226" t="s">
         <v>277</v>
       </c>
-      <c r="B57" s="137"/>
-      <c r="C57" s="137"/>
-      <c r="D57" s="137"/>
-      <c r="E57" s="137"/>
-      <c r="F57" s="137"/>
-      <c r="G57" s="137"/>
+      <c r="B57" s="224"/>
+      <c r="C57" s="224"/>
+      <c r="D57" s="224"/>
+      <c r="E57" s="224"/>
+      <c r="F57" s="224"/>
+      <c r="G57" s="224"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -6537,20 +6558,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="228" t="s">
         <v>222</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
+      <c r="B1" s="224"/>
+      <c r="C1" s="224"/>
+      <c r="D1" s="224"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="225" t="s">
         <v>223</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="B2" s="224"/>
+      <c r="C2" s="224"/>
+      <c r="D2" s="224"/>
     </row>
     <row r="3" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6703,462 +6724,462 @@
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="42" style="144" customWidth="1"/>
-    <col min="2" max="2" width="16" style="144" customWidth="1"/>
-    <col min="3" max="3" width="47.83203125" style="144" customWidth="1"/>
-    <col min="4" max="4" width="3" style="144" customWidth="1"/>
-    <col min="5" max="5" width="42" style="144" customWidth="1"/>
-    <col min="6" max="6" width="16" style="144" customWidth="1"/>
-    <col min="7" max="7" width="36" style="144" customWidth="1"/>
-    <col min="8" max="16384" width="8.83203125" style="144"/>
+    <col min="1" max="1" width="42" style="131" customWidth="1"/>
+    <col min="2" max="2" width="16" style="131" customWidth="1"/>
+    <col min="3" max="3" width="47.83203125" style="131" customWidth="1"/>
+    <col min="4" max="4" width="3" style="131" customWidth="1"/>
+    <col min="5" max="5" width="42" style="131" customWidth="1"/>
+    <col min="6" max="6" width="16" style="131" customWidth="1"/>
+    <col min="7" max="7" width="36" style="131" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="131"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="233" t="s">
         <v>310</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
+      <c r="B1" s="231"/>
+      <c r="C1" s="231"/>
+      <c r="D1" s="231"/>
+      <c r="E1" s="231"/>
+      <c r="F1" s="231"/>
+      <c r="G1" s="231"/>
     </row>
     <row r="2" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="170" t="s">
+      <c r="A2" s="232" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="145"/>
-      <c r="C2" s="145"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="145"/>
-      <c r="F2" s="145"/>
-      <c r="G2" s="145"/>
+      <c r="B2" s="231"/>
+      <c r="C2" s="231"/>
+      <c r="D2" s="231"/>
+      <c r="E2" s="231"/>
+      <c r="F2" s="231"/>
+      <c r="G2" s="231"/>
     </row>
     <row r="3" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="169" t="s">
+      <c r="A4" s="153" t="s">
         <v>120</v>
       </c>
-      <c r="B4" s="168"/>
-      <c r="C4" s="168"/>
-      <c r="E4" s="169" t="s">
+      <c r="B4" s="152"/>
+      <c r="C4" s="152"/>
+      <c r="E4" s="153" t="s">
         <v>121</v>
       </c>
-      <c r="F4" s="168"/>
-      <c r="G4" s="168"/>
+      <c r="F4" s="152"/>
+      <c r="G4" s="152"/>
     </row>
     <row r="5" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="151" t="s">
         <v>122</v>
       </c>
-      <c r="B5" s="167" t="s">
+      <c r="B5" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="167" t="s">
+      <c r="C5" s="151" t="s">
         <v>124</v>
       </c>
-      <c r="E5" s="167" t="s">
+      <c r="E5" s="151" t="s">
         <v>122</v>
       </c>
-      <c r="F5" s="167" t="s">
+      <c r="F5" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="G5" s="167" t="s">
+      <c r="G5" s="151" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="153" t="s">
+      <c r="A6" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="166">
+      <c r="B6" s="150">
         <v>46.31</v>
       </c>
-      <c r="C6" s="151" t="s">
+      <c r="C6" s="135" t="s">
         <v>126</v>
       </c>
-      <c r="E6" s="153" t="s">
+      <c r="E6" s="137" t="s">
         <v>127</v>
       </c>
-      <c r="F6" s="157">
+      <c r="F6" s="141">
         <v>130000</v>
       </c>
-      <c r="G6" s="151" t="s">
+      <c r="G6" s="135" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="150" t="s">
+      <c r="A7" s="134" t="s">
         <v>129</v>
       </c>
-      <c r="B7" s="165">
+      <c r="B7" s="149">
         <v>2868</v>
       </c>
-      <c r="C7" s="148" t="s">
+      <c r="C7" s="132" t="s">
         <v>245</v>
       </c>
-      <c r="E7" s="155" t="s">
+      <c r="E7" s="139" t="s">
         <v>131</v>
       </c>
-      <c r="F7" s="154">
+      <c r="F7" s="138">
         <v>58893</v>
       </c>
-      <c r="G7" s="148" t="s">
+      <c r="G7" s="132" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="153" t="s">
+      <c r="A8" s="137" t="s">
         <v>133</v>
       </c>
-      <c r="B8" s="152">
+      <c r="B8" s="136">
         <f>B6*B7</f>
         <v>132817.08000000002</v>
       </c>
-      <c r="C8" s="151" t="s">
+      <c r="C8" s="135" t="s">
         <v>134</v>
       </c>
-      <c r="E8" s="159" t="s">
+      <c r="E8" s="143" t="s">
         <v>135</v>
       </c>
-      <c r="F8" s="157">
+      <c r="F8" s="141">
         <v>60895</v>
       </c>
-      <c r="G8" s="151" t="s">
+      <c r="G8" s="135" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="150" t="s">
+      <c r="A9" s="134" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="154">
+      <c r="B9" s="138">
         <v>45922</v>
       </c>
-      <c r="C9" s="148" t="s">
+      <c r="C9" s="132" t="s">
         <v>138</v>
       </c>
-      <c r="E9" s="155" t="s">
+      <c r="E9" s="139" t="s">
         <v>139</v>
       </c>
-      <c r="F9" s="154">
+      <c r="F9" s="138">
         <v>3500</v>
       </c>
-      <c r="G9" s="148" t="s">
+      <c r="G9" s="132" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="153" t="s">
+      <c r="A10" s="137" t="s">
         <v>141</v>
       </c>
-      <c r="B10" s="152">
+      <c r="B10" s="136">
         <f>B8+B9</f>
         <v>178739.08000000002</v>
       </c>
-      <c r="C10" s="151" t="s">
+      <c r="C10" s="135" t="s">
         <v>134</v>
       </c>
-      <c r="E10" s="159" t="s">
+      <c r="E10" s="143" t="s">
         <v>142</v>
       </c>
-      <c r="F10" s="152">
+      <c r="F10" s="136">
         <f>F6-F7-F8-F9</f>
         <v>6712</v>
       </c>
-      <c r="G10" s="151" t="s">
+      <c r="G10" s="135" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="155"/>
-      <c r="C11" s="148"/>
-      <c r="E11" s="155"/>
-      <c r="G11" s="148"/>
+      <c r="A11" s="139"/>
+      <c r="C11" s="132"/>
+      <c r="E11" s="139"/>
+      <c r="G11" s="132"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="153" t="s">
+      <c r="A12" s="137" t="s">
         <v>246</v>
       </c>
-      <c r="B12" s="157">
+      <c r="B12" s="141">
         <v>-2193</v>
       </c>
-      <c r="C12" s="151" t="s">
+      <c r="C12" s="135" t="s">
         <v>247</v>
       </c>
-      <c r="E12" s="153" t="s">
+      <c r="E12" s="137" t="s">
         <v>145</v>
       </c>
-      <c r="F12" s="164">
+      <c r="F12" s="148">
         <v>1274</v>
       </c>
-      <c r="G12" s="151" t="s">
+      <c r="G12" s="135" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="150" t="s">
+      <c r="A13" s="134" t="s">
         <v>248</v>
       </c>
-      <c r="B13" s="154">
+      <c r="B13" s="138">
         <v>4894</v>
       </c>
-      <c r="C13" s="148" t="s">
+      <c r="C13" s="132" t="s">
         <v>249</v>
       </c>
-      <c r="E13" s="150" t="s">
+      <c r="E13" s="134" t="s">
         <v>149</v>
       </c>
-      <c r="F13" s="163">
+      <c r="F13" s="147">
         <f>F8/F12</f>
         <v>47.798273155416013</v>
       </c>
-      <c r="G13" s="148" t="s">
+      <c r="G13" s="132" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="153" t="s">
+      <c r="A14" s="137" t="s">
         <v>250</v>
       </c>
-      <c r="B14" s="157">
+      <c r="B14" s="141">
         <v>2549</v>
       </c>
-      <c r="C14" s="151" t="s">
+      <c r="C14" s="135" t="s">
         <v>249</v>
       </c>
-      <c r="E14" s="155"/>
-      <c r="G14" s="148"/>
+      <c r="E14" s="139"/>
+      <c r="G14" s="132"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="150" t="s">
+      <c r="A15" s="134" t="s">
         <v>251</v>
       </c>
-      <c r="B15" s="154">
+      <c r="B15" s="138">
         <v>2404</v>
       </c>
-      <c r="C15" s="148" t="s">
+      <c r="C15" s="132" t="s">
         <v>249</v>
       </c>
-      <c r="E15" s="153" t="s">
+      <c r="E15" s="137" t="s">
         <v>155</v>
       </c>
-      <c r="F15" s="157">
+      <c r="F15" s="141">
         <v>49000</v>
       </c>
-      <c r="G15" s="151" t="s">
+      <c r="G15" s="135" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="153" t="s">
+      <c r="A16" s="137" t="s">
         <v>252</v>
       </c>
-      <c r="B16" s="157">
+      <c r="B16" s="141">
         <v>875</v>
       </c>
-      <c r="C16" s="151" t="s">
+      <c r="C16" s="135" t="s">
         <v>253</v>
       </c>
-      <c r="E16" s="150" t="s">
+      <c r="E16" s="134" t="s">
         <v>159</v>
       </c>
-      <c r="F16" s="162">
+      <c r="F16" s="146">
         <v>5.5E-2</v>
       </c>
-      <c r="G16" s="148" t="s">
+      <c r="G16" s="132" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="150" t="s">
+      <c r="A17" s="134" t="s">
         <v>254</v>
       </c>
-      <c r="B17" s="160" t="str">
+      <c r="B17" s="144" t="str">
         <f>IF(B12&lt;0,"N/A – neg. base",((B16/B12)^(1/4)-1))</f>
         <v>N/A – neg. base</v>
       </c>
-      <c r="C17" s="148" t="s">
+      <c r="C17" s="132" t="s">
         <v>256</v>
       </c>
-      <c r="E17" s="153" t="s">
+      <c r="E17" s="137" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="161">
+      <c r="F17" s="145">
         <v>0.2319</v>
       </c>
-      <c r="G17" s="151" t="s">
+      <c r="G17" s="135" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="155"/>
-      <c r="C18" s="148"/>
-      <c r="E18" s="150" t="s">
+      <c r="A18" s="139"/>
+      <c r="C18" s="132"/>
+      <c r="E18" s="134" t="s">
         <v>164</v>
       </c>
-      <c r="F18" s="149">
+      <c r="F18" s="133">
         <f>F15*F16*(1-F17)</f>
         <v>2070.0295000000001</v>
       </c>
-      <c r="G18" s="148" t="s">
+      <c r="G18" s="132" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="153" t="s">
+      <c r="A19" s="137" t="s">
         <v>258</v>
       </c>
-      <c r="B19" s="161">
+      <c r="B19" s="145">
         <v>0.04</v>
       </c>
-      <c r="C19" s="151" t="s">
+      <c r="C19" s="135" t="s">
         <v>284</v>
       </c>
-      <c r="E19" s="155"/>
-      <c r="G19" s="148"/>
+      <c r="E19" s="139"/>
+      <c r="G19" s="132"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="155" t="s">
+      <c r="A20" s="139" t="s">
         <v>260</v>
       </c>
-      <c r="B20" s="160">
+      <c r="B20" s="144">
         <f>B19</f>
         <v>0.04</v>
       </c>
-      <c r="C20" s="148" t="s">
+      <c r="C20" s="132" t="s">
         <v>261</v>
       </c>
-      <c r="E20" s="153" t="s">
+      <c r="E20" s="137" t="s">
         <v>168</v>
       </c>
-      <c r="F20" s="157">
+      <c r="F20" s="141">
         <v>500</v>
       </c>
-      <c r="G20" s="151" t="s">
+      <c r="G20" s="135" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="159" t="s">
+      <c r="A21" s="143" t="s">
         <v>262</v>
       </c>
-      <c r="B21" s="158">
+      <c r="B21" s="142">
         <f>B19</f>
         <v>0.04</v>
       </c>
-      <c r="C21" s="151" t="s">
+      <c r="C21" s="135" t="s">
         <v>261</v>
       </c>
-      <c r="E21" s="150" t="s">
+      <c r="E21" s="134" t="s">
         <v>170</v>
       </c>
-      <c r="F21" s="154">
+      <c r="F21" s="138">
         <v>800</v>
       </c>
-      <c r="G21" s="148" t="s">
+      <c r="G21" s="132" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="155"/>
-      <c r="C22" s="148"/>
-      <c r="E22" s="153" t="s">
+      <c r="A22" s="139"/>
+      <c r="C22" s="132"/>
+      <c r="E22" s="137" t="s">
         <v>174</v>
       </c>
-      <c r="F22" s="157">
+      <c r="F22" s="141">
         <v>1200</v>
       </c>
-      <c r="G22" s="151" t="s">
+      <c r="G22" s="135" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="150" t="s">
+      <c r="A23" s="134" t="s">
         <v>165</v>
       </c>
-      <c r="B23" s="154">
+      <c r="B23" s="138">
         <v>11497</v>
       </c>
-      <c r="C23" s="148" t="s">
+      <c r="C23" s="132" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="153" t="s">
+      <c r="A24" s="137" t="s">
         <v>167</v>
       </c>
-      <c r="B24" s="156">
+      <c r="B24" s="140">
         <f>B23/B7</f>
         <v>4.0087168758716878</v>
       </c>
-      <c r="C24" s="151" t="s">
+      <c r="C24" s="135" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="155"/>
-      <c r="C25" s="148"/>
+      <c r="A25" s="139"/>
+      <c r="C25" s="132"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="150" t="s">
+      <c r="A26" s="134" t="s">
         <v>178</v>
       </c>
-      <c r="B26" s="154">
+      <c r="B26" s="138">
         <v>17800</v>
       </c>
-      <c r="C26" s="148" t="s">
+      <c r="C26" s="132" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="153" t="s">
+      <c r="A27" s="137" t="s">
         <v>180</v>
       </c>
-      <c r="B27" s="152">
+      <c r="B27" s="136">
         <f>B26*(1+B20)</f>
         <v>18512</v>
       </c>
-      <c r="C27" s="151" t="s">
+      <c r="C27" s="135" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="150" t="s">
+      <c r="A28" s="134" t="s">
         <v>182</v>
       </c>
-      <c r="B28" s="149">
+      <c r="B28" s="133">
         <f>B27*(1+B21)</f>
         <v>19252.48</v>
       </c>
-      <c r="C28" s="148" t="s">
+      <c r="C28" s="132" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="38" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="147" t="s">
+      <c r="A29" s="234" t="s">
         <v>285</v>
       </c>
-      <c r="B29" s="145"/>
-      <c r="C29" s="145"/>
+      <c r="B29" s="231"/>
+      <c r="C29" s="231"/>
     </row>
     <row r="30" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="145"/>
-      <c r="B30" s="145"/>
-      <c r="C30" s="145"/>
+      <c r="A30" s="231"/>
+      <c r="B30" s="231"/>
+      <c r="C30" s="231"/>
     </row>
     <row r="31" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="146" t="s">
+      <c r="A32" s="230" t="s">
         <v>183</v>
       </c>
-      <c r="B32" s="145"/>
-      <c r="C32" s="145"/>
-      <c r="D32" s="145"/>
-      <c r="E32" s="145"/>
-      <c r="F32" s="145"/>
-      <c r="G32" s="145"/>
+      <c r="B32" s="231"/>
+      <c r="C32" s="231"/>
+      <c r="D32" s="231"/>
+      <c r="E32" s="231"/>
+      <c r="F32" s="231"/>
+      <c r="G32" s="231"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -7176,943 +7197,943 @@
   <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="45.83203125" style="144" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="15.6640625" style="144" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5" style="144" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" style="144" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.83203125" style="144"/>
+    <col min="1" max="1" width="45.83203125" style="131" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.6640625" style="131" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5" style="131" customWidth="1"/>
+    <col min="5" max="5" width="6.6640625" style="131" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="131"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="233" t="s">
         <v>311</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
+      <c r="B1" s="231"/>
+      <c r="C1" s="231"/>
+      <c r="D1" s="231"/>
+      <c r="E1" s="231"/>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="170" t="s">
+      <c r="A2" s="232" t="s">
         <v>287</v>
       </c>
-      <c r="B2" s="145"/>
-      <c r="C2" s="145"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="145"/>
+      <c r="B2" s="231"/>
+      <c r="C2" s="231"/>
+      <c r="D2" s="231"/>
+      <c r="E2" s="231"/>
     </row>
     <row r="3" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="189" t="s">
+      <c r="A4" s="158" t="s">
         <v>186</v>
       </c>
-      <c r="B4" s="189" t="s">
+      <c r="B4" s="158" t="s">
         <v>187</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="158" t="s">
         <v>188</v>
       </c>
-      <c r="D4" s="189" t="s">
+      <c r="D4" s="158" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="153" t="s">
         <v>190</v>
       </c>
-      <c r="B5" s="168"/>
-      <c r="C5" s="168"/>
-      <c r="D5" s="168"/>
+      <c r="B5" s="152"/>
+      <c r="C5" s="152"/>
+      <c r="D5" s="152"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="159" t="s">
+      <c r="A6" s="143" t="s">
         <v>191</v>
       </c>
-      <c r="B6" s="188">
-        <f>'Assumptions (3)'!B7</f>
+      <c r="B6" s="170">
+        <f>'Assumptions (VF)'!B7</f>
         <v>2868</v>
       </c>
-      <c r="C6" s="188">
-        <f>'Assumptions (3)'!B7</f>
+      <c r="C6" s="170">
+        <f>'Assumptions (VF)'!B7</f>
         <v>2868</v>
       </c>
-      <c r="D6" s="188">
-        <f>'Assumptions (3)'!B7</f>
+      <c r="D6" s="170">
+        <f>'Assumptions (VF)'!B7</f>
         <v>2868</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="155" t="s">
+      <c r="A7" s="139" t="s">
         <v>192</v>
       </c>
-      <c r="B7" s="186">
-        <f>'Assumptions (3)'!F12</f>
+      <c r="B7" s="168">
+        <f>'Assumptions (VF)'!F12</f>
         <v>1274</v>
       </c>
-      <c r="C7" s="186">
-        <f>'Assumptions (3)'!F12</f>
+      <c r="C7" s="168">
+        <f>'Assumptions (VF)'!F12</f>
         <v>1274</v>
       </c>
-      <c r="D7" s="186">
-        <f>'Assumptions (3)'!F12</f>
+      <c r="D7" s="168">
+        <f>'Assumptions (VF)'!F12</f>
         <v>1274</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="153" t="s">
+      <c r="A8" s="137" t="s">
         <v>193</v>
       </c>
-      <c r="B8" s="187">
+      <c r="B8" s="169">
         <f>B6+B7</f>
         <v>4142</v>
       </c>
-      <c r="C8" s="187">
+      <c r="C8" s="169">
         <f>C6+C7</f>
         <v>4142</v>
       </c>
-      <c r="D8" s="187">
+      <c r="D8" s="169">
         <f>D6+D7</f>
         <v>4142</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="169" t="s">
+      <c r="A10" s="153" t="s">
         <v>194</v>
       </c>
-      <c r="B10" s="168"/>
-      <c r="C10" s="168"/>
-      <c r="D10" s="168"/>
+      <c r="B10" s="152"/>
+      <c r="C10" s="152"/>
+      <c r="D10" s="152"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="159" t="s">
+      <c r="A11" s="143" t="s">
         <v>195</v>
       </c>
-      <c r="B11" s="185">
-        <f>'Assumptions (3)'!B23</f>
+      <c r="B11" s="167">
+        <f>'Assumptions (VF)'!B23</f>
         <v>11497</v>
       </c>
-      <c r="C11" s="185">
-        <f>B11*(1+'Assumptions (3)'!B20)</f>
+      <c r="C11" s="167">
+        <f>B11*(1+'Assumptions (VF)'!B20)</f>
         <v>11956.880000000001</v>
       </c>
-      <c r="D11" s="185">
-        <f>C11*(1+'Assumptions (3)'!B21)</f>
+      <c r="D11" s="167">
+        <f>C11*(1+'Assumptions (VF)'!B21)</f>
         <v>12435.155200000001</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="155" t="s">
+      <c r="A12" s="139" t="s">
         <v>191</v>
       </c>
-      <c r="B12" s="186">
-        <f>'Assumptions (3)'!B7</f>
+      <c r="B12" s="168">
+        <f>'Assumptions (VF)'!B7</f>
         <v>2868</v>
       </c>
-      <c r="C12" s="186">
-        <f>'Assumptions (3)'!B7</f>
+      <c r="C12" s="168">
+        <f>'Assumptions (VF)'!B7</f>
         <v>2868</v>
       </c>
-      <c r="D12" s="186">
-        <f>'Assumptions (3)'!B7</f>
+      <c r="D12" s="168">
+        <f>'Assumptions (VF)'!B7</f>
         <v>2868</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="153" t="s">
+      <c r="A13" s="137" t="s">
         <v>196</v>
       </c>
-      <c r="B13" s="156">
+      <c r="B13" s="140">
         <f>B11/B12</f>
         <v>4.0087168758716878</v>
       </c>
-      <c r="C13" s="156">
+      <c r="C13" s="140">
         <f>C11/C12</f>
         <v>4.1690655509065557</v>
       </c>
-      <c r="D13" s="156">
+      <c r="D13" s="140">
         <f>D11/D12</f>
         <v>4.3358281729428176</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="169" t="s">
+      <c r="A15" s="153" t="s">
         <v>197</v>
       </c>
-      <c r="B15" s="168"/>
-      <c r="C15" s="168"/>
-      <c r="D15" s="168"/>
+      <c r="B15" s="152"/>
+      <c r="C15" s="152"/>
+      <c r="D15" s="152"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="159" t="s">
+      <c r="A16" s="143" t="s">
         <v>195</v>
       </c>
-      <c r="B16" s="152">
+      <c r="B16" s="136">
         <f>B11</f>
         <v>11497</v>
       </c>
-      <c r="C16" s="152">
+      <c r="C16" s="136">
         <f>C11</f>
         <v>11956.880000000001</v>
       </c>
-      <c r="D16" s="152">
+      <c r="D16" s="136">
         <f>D11</f>
         <v>12435.155200000001</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="155" t="s">
+      <c r="A17" s="139" t="s">
         <v>198</v>
       </c>
-      <c r="B17" s="184">
-        <f>'Assumptions (3)'!B26-'Assumptions (3)'!B23</f>
+      <c r="B17" s="166">
+        <f>'Assumptions (VF)'!B26-'Assumptions (VF)'!B23</f>
         <v>6303</v>
       </c>
-      <c r="C17" s="184">
-        <f>'Assumptions (3)'!B27-B11*(1+'Assumptions (3)'!B20)</f>
+      <c r="C17" s="166">
+        <f>'Assumptions (VF)'!B27-B11*(1+'Assumptions (VF)'!B20)</f>
         <v>6555.119999999999</v>
       </c>
-      <c r="D17" s="184">
-        <f>'Assumptions (3)'!B28-C11*(1+'Assumptions (3)'!B21)</f>
+      <c r="D17" s="166">
+        <f>'Assumptions (VF)'!B28-C11*(1+'Assumptions (VF)'!B21)</f>
         <v>6817.3247999999985</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="159" t="s">
+      <c r="A18" s="143" t="s">
         <v>199</v>
       </c>
-      <c r="B18" s="185">
-        <f>-'Assumptions (3)'!F18</f>
+      <c r="B18" s="167">
+        <f>-'Assumptions (VF)'!F18</f>
         <v>-2070.0295000000001</v>
       </c>
-      <c r="C18" s="185">
-        <f>-'Assumptions (3)'!F18</f>
+      <c r="C18" s="167">
+        <f>-'Assumptions (VF)'!F18</f>
         <v>-2070.0295000000001</v>
       </c>
-      <c r="D18" s="185">
-        <f>-'Assumptions (3)'!F18</f>
+      <c r="D18" s="167">
+        <f>-'Assumptions (VF)'!F18</f>
         <v>-2070.0295000000001</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="155" t="s">
+      <c r="A19" s="139" t="s">
         <v>200</v>
       </c>
-      <c r="B19" s="184">
-        <f>'Assumptions (3)'!F20*(1-'Assumptions (3)'!F17)</f>
+      <c r="B19" s="166">
+        <f>'Assumptions (VF)'!F20*(1-'Assumptions (VF)'!F17)</f>
         <v>384.05</v>
       </c>
-      <c r="C19" s="184">
-        <f>'Assumptions (3)'!F20*(1-'Assumptions (3)'!F17)*1.1</f>
+      <c r="C19" s="166">
+        <f>'Assumptions (VF)'!F20*(1-'Assumptions (VF)'!F17)*1.1</f>
         <v>422.45500000000004</v>
       </c>
-      <c r="D19" s="184">
-        <f>'Assumptions (3)'!F20*(1-'Assumptions (3)'!F17)*1.2</f>
+      <c r="D19" s="166">
+        <f>'Assumptions (VF)'!F20*(1-'Assumptions (VF)'!F17)*1.2</f>
         <v>460.86</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="159" t="s">
+      <c r="A20" s="143" t="s">
         <v>201</v>
       </c>
-      <c r="B20" s="185">
-        <f>-'Assumptions (3)'!F21</f>
+      <c r="B20" s="167">
+        <f>-'Assumptions (VF)'!F21</f>
         <v>-800</v>
       </c>
-      <c r="C20" s="185">
-        <f>-'Assumptions (3)'!F21</f>
+      <c r="C20" s="167">
+        <f>-'Assumptions (VF)'!F21</f>
         <v>-800</v>
       </c>
-      <c r="D20" s="185">
-        <f>-'Assumptions (3)'!F21</f>
+      <c r="D20" s="167">
+        <f>-'Assumptions (VF)'!F21</f>
         <v>-800</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="155" t="s">
+      <c r="A21" s="139" t="s">
         <v>202</v>
       </c>
-      <c r="B21" s="184">
-        <f>-'Assumptions (3)'!F22</f>
+      <c r="B21" s="166">
+        <f>-'Assumptions (VF)'!F22</f>
         <v>-1200</v>
       </c>
-      <c r="C21" s="149">
+      <c r="C21" s="133">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="D21" s="149">
+      <c r="D21" s="133">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="153" t="s">
+      <c r="A22" s="137" t="s">
         <v>203</v>
       </c>
-      <c r="B22" s="152">
+      <c r="B22" s="136">
         <f>SUM(B16:B21)</f>
         <v>14114.020499999999</v>
       </c>
-      <c r="C22" s="152">
+      <c r="C22" s="136">
         <f>SUM(C16:C21)</f>
         <v>16064.425500000001</v>
       </c>
-      <c r="D22" s="152">
+      <c r="D22" s="136">
         <f>SUM(D16:D21)</f>
         <v>16843.3105</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="169" t="s">
+      <c r="A24" s="153" t="s">
         <v>204</v>
       </c>
-      <c r="B24" s="168"/>
-      <c r="C24" s="168"/>
-      <c r="D24" s="168"/>
+      <c r="B24" s="152"/>
+      <c r="C24" s="152"/>
+      <c r="D24" s="152"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="159" t="s">
+      <c r="A25" s="143" t="s">
         <v>205</v>
       </c>
-      <c r="B25" s="152">
+      <c r="B25" s="136">
         <f>B22</f>
         <v>14114.020499999999</v>
       </c>
-      <c r="C25" s="152">
+      <c r="C25" s="136">
         <f>C22</f>
         <v>16064.425500000001</v>
       </c>
-      <c r="D25" s="152">
+      <c r="D25" s="136">
         <f>D22</f>
         <v>16843.3105</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="155" t="s">
+      <c r="A26" s="139" t="s">
         <v>193</v>
       </c>
-      <c r="B26" s="183">
+      <c r="B26" s="165">
         <f>B8</f>
         <v>4142</v>
       </c>
-      <c r="C26" s="183">
+      <c r="C26" s="165">
         <f>C8</f>
         <v>4142</v>
       </c>
-      <c r="D26" s="183">
+      <c r="D26" s="165">
         <f>D8</f>
         <v>4142</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="153" t="s">
+      <c r="A27" s="137" t="s">
         <v>206</v>
       </c>
-      <c r="B27" s="156">
+      <c r="B27" s="140">
         <f>B25/B26</f>
         <v>3.4075375422501204</v>
       </c>
-      <c r="C27" s="156">
+      <c r="C27" s="140">
         <f>C25/C26</f>
         <v>3.8784223804925162</v>
       </c>
-      <c r="D27" s="156">
+      <c r="D27" s="140">
         <f>D25/D26</f>
         <v>4.066468010622887</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="155"/>
-      <c r="B28" s="182"/>
-      <c r="C28" s="182"/>
-      <c r="D28" s="182"/>
+      <c r="A28" s="139"/>
+      <c r="B28" s="164"/>
+      <c r="C28" s="164"/>
+      <c r="D28" s="164"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="159" t="s">
+      <c r="A29" s="143" t="s">
         <v>207</v>
       </c>
-      <c r="B29" s="156">
+      <c r="B29" s="140">
         <f>B13</f>
         <v>4.0087168758716878</v>
       </c>
-      <c r="C29" s="156">
+      <c r="C29" s="140">
         <f>C13</f>
         <v>4.1690655509065557</v>
       </c>
-      <c r="D29" s="156">
+      <c r="D29" s="140">
         <f>D13</f>
         <v>4.3358281729428176</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="155" t="s">
+      <c r="A30" s="139" t="s">
         <v>208</v>
       </c>
-      <c r="B30" s="181">
+      <c r="B30" s="163">
         <f>B27</f>
         <v>3.4075375422501204</v>
       </c>
-      <c r="C30" s="181">
+      <c r="C30" s="163">
         <f>C27</f>
         <v>3.8784223804925162</v>
       </c>
-      <c r="D30" s="181">
+      <c r="D30" s="163">
         <f>D27</f>
         <v>4.066468010622887</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="153" t="s">
+      <c r="A31" s="137" t="s">
         <v>209</v>
       </c>
-      <c r="B31" s="180">
+      <c r="B31" s="162">
         <f>B30-B29</f>
         <v>-0.60117933362156739</v>
       </c>
-      <c r="C31" s="180">
+      <c r="C31" s="162">
         <f>C30-C29</f>
         <v>-0.29064317041403953</v>
       </c>
-      <c r="D31" s="180">
+      <c r="D31" s="162">
         <f>D30-D29</f>
         <v>-0.26936016231993065</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="153" t="s">
+      <c r="A32" s="137" t="s">
         <v>210</v>
       </c>
-      <c r="B32" s="179">
+      <c r="B32" s="161">
         <f>B31/B29</f>
         <v>-0.149968020251079</v>
       </c>
-      <c r="C32" s="179">
+      <c r="C32" s="161">
         <f>C31/C29</f>
         <v>-6.9714224174489095E-2</v>
       </c>
-      <c r="D32" s="179">
+      <c r="D32" s="161">
         <f>D31/D29</f>
         <v>-6.2124270514417143E-2</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="146" t="s">
+      <c r="A34" s="230" t="s">
         <v>267</v>
       </c>
-      <c r="B34" s="145"/>
-      <c r="C34" s="145"/>
-      <c r="D34" s="145"/>
-      <c r="E34" s="145"/>
+      <c r="B34" s="231"/>
+      <c r="C34" s="231"/>
+      <c r="D34" s="231"/>
+      <c r="E34" s="231"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="171" t="s">
+      <c r="A35" s="233" t="s">
         <v>211</v>
       </c>
-      <c r="B35" s="145"/>
-      <c r="C35" s="145"/>
-      <c r="D35" s="145"/>
-      <c r="E35" s="145"/>
-      <c r="F35" s="145"/>
-      <c r="G35" s="145"/>
+      <c r="B35" s="231"/>
+      <c r="C35" s="231"/>
+      <c r="D35" s="231"/>
+      <c r="E35" s="231"/>
+      <c r="F35" s="231"/>
+      <c r="G35" s="231"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="170" t="s">
+      <c r="A36" s="232" t="s">
         <v>288</v>
       </c>
-      <c r="B36" s="145"/>
-      <c r="C36" s="145"/>
-      <c r="D36" s="145"/>
-      <c r="E36" s="145"/>
-      <c r="F36" s="145"/>
-      <c r="G36" s="145"/>
+      <c r="B36" s="231"/>
+      <c r="C36" s="231"/>
+      <c r="D36" s="231"/>
+      <c r="E36" s="231"/>
+      <c r="F36" s="231"/>
+      <c r="G36" s="231"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="176" t="s">
+      <c r="A38" s="235" t="s">
         <v>269</v>
       </c>
-      <c r="B38" s="145"/>
-      <c r="C38" s="145"/>
-      <c r="D38" s="145"/>
-      <c r="E38" s="145"/>
-      <c r="F38" s="145"/>
-      <c r="G38" s="145"/>
+      <c r="B38" s="231"/>
+      <c r="C38" s="231"/>
+      <c r="D38" s="231"/>
+      <c r="E38" s="231"/>
+      <c r="F38" s="231"/>
+      <c r="G38" s="231"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="167" t="s">
+      <c r="A39" s="151" t="s">
         <v>270</v>
       </c>
-      <c r="B39" s="175">
+      <c r="B39" s="157">
         <v>0.02</v>
       </c>
-      <c r="C39" s="175">
+      <c r="C39" s="157">
         <v>0.03</v>
       </c>
-      <c r="D39" s="167" t="s">
+      <c r="D39" s="151" t="s">
         <v>290</v>
       </c>
-      <c r="E39" s="175">
+      <c r="E39" s="157">
         <v>0.05</v>
       </c>
-      <c r="F39" s="175">
+      <c r="F39" s="157">
         <v>0.06</v>
       </c>
-      <c r="G39" s="175">
+      <c r="G39" s="157">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="173">
+      <c r="A40" s="155">
         <v>0</v>
       </c>
-      <c r="B40" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.02)^2+0*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="B40" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.02)^2+0*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>3.7781483582810234</v>
       </c>
-      <c r="C40" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.03)^2+0*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="C40" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.03)^2+0*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>3.8662458957025589</v>
       </c>
-      <c r="D40" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.04)^2+0*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="D40" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.04)^2+0*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>3.9552029212940614</v>
       </c>
-      <c r="E40" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.05)^2+0*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="E40" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.05)^2+0*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.0450194350555284</v>
       </c>
-      <c r="F40" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.06)^2+0*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="F40" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.06)^2+0*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.1356954369869632</v>
       </c>
-      <c r="G40" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.07)^2+0*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="G40" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.07)^2+0*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.227230927088363</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="173">
+      <c r="A41" s="155">
         <v>250</v>
       </c>
-      <c r="B41" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.02)^2+250*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="B41" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.02)^2+250*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>3.8337809029454366</v>
       </c>
-      <c r="C41" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.03)^2+250*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="C41" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.03)^2+250*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>3.9218784403669726</v>
       </c>
-      <c r="D41" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.04)^2+250*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="D41" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.04)^2+250*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.0108354659584746</v>
       </c>
-      <c r="E41" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.05)^2+250*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="E41" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.05)^2+250*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.1006519797199417</v>
       </c>
-      <c r="F41" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.06)^2+250*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="F41" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.06)^2+250*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.1913279816513764</v>
       </c>
-      <c r="G41" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.07)^2+250*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="G41" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.07)^2+250*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.2828634717527763</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="173">
+      <c r="A42" s="155">
         <v>500</v>
       </c>
-      <c r="B42" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.02)^2+500*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="B42" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.02)^2+500*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>3.8894134476098499</v>
       </c>
-      <c r="C42" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.03)^2+500*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="C42" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.03)^2+500*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>3.9775109850313859</v>
       </c>
-      <c r="D42" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.04)^2+500*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="D42" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.04)^2+500*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.0664680106228879</v>
       </c>
-      <c r="E42" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.05)^2+500*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="E42" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.05)^2+500*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.1562845243843558</v>
       </c>
-      <c r="F42" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.06)^2+500*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="F42" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.06)^2+500*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.2469605263157897</v>
       </c>
-      <c r="G42" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.07)^2+500*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="G42" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.07)^2+500*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.3384960164171904</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="173">
+      <c r="A43" s="155">
         <v>750</v>
       </c>
-      <c r="B43" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.02)^2+750*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="B43" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.02)^2+750*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>3.9450459922742636</v>
       </c>
-      <c r="C43" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.03)^2+750*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="C43" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.03)^2+750*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.0331435296957991</v>
       </c>
-      <c r="D43" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.04)^2+750*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="D43" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.04)^2+750*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.122100555287302</v>
       </c>
-      <c r="E43" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.05)^2+750*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="E43" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.05)^2+750*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.2119170690487691</v>
       </c>
-      <c r="F43" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.06)^2+750*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="F43" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.06)^2+750*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.3025930709802029</v>
       </c>
-      <c r="G43" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.07)^2+750*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="G43" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.07)^2+750*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.3941285610816037</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" s="173">
+      <c r="A44" s="155">
         <v>1000</v>
       </c>
-      <c r="B44" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.02)^2+1000*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="B44" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.02)^2+1000*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.0006785369386773</v>
       </c>
-      <c r="C44" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.03)^2+1000*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="C44" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.03)^2+1000*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.0887760743602124</v>
       </c>
-      <c r="D44" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.04)^2+1000*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="D44" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.04)^2+1000*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.1777330999517153</v>
       </c>
-      <c r="E44" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.05)^2+1000*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="E44" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.05)^2+1000*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.2675496137131823</v>
       </c>
-      <c r="F44" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.06)^2+1000*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="F44" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.06)^2+1000*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.3582256156446171</v>
       </c>
-      <c r="G44" s="178">
-        <f>('Assumptions (3)'!B26*(1+0.07)^2+1000*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="G44" s="160">
+        <f>('Assumptions (VF)'!B26*(1+0.07)^2+1000*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.4497611057460169</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="173">
+      <c r="A45" s="155">
         <v>1500</v>
       </c>
-      <c r="B45" s="177">
-        <f>('Assumptions (3)'!B26*(1+0.02)^2+1500*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="B45" s="159">
+        <f>('Assumptions (VF)'!B26*(1+0.02)^2+1500*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.1119436262675029</v>
       </c>
-      <c r="C45" s="177">
-        <f>('Assumptions (3)'!B26*(1+0.03)^2+1500*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="C45" s="159">
+        <f>('Assumptions (VF)'!B26*(1+0.03)^2+1500*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.2000411636890389</v>
       </c>
-      <c r="D45" s="177">
-        <f>('Assumptions (3)'!B26*(1+0.04)^2+1500*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="D45" s="159">
+        <f>('Assumptions (VF)'!B26*(1+0.04)^2+1500*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.2889981892805418</v>
       </c>
-      <c r="E45" s="177">
-        <f>('Assumptions (3)'!B26*(1+0.05)^2+1500*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="E45" s="159">
+        <f>('Assumptions (VF)'!B26*(1+0.05)^2+1500*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.3788147030420088</v>
       </c>
-      <c r="F45" s="177">
-        <f>('Assumptions (3)'!B26*(1+0.06)^2+1500*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="F45" s="159">
+        <f>('Assumptions (VF)'!B26*(1+0.06)^2+1500*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.4694907049734436</v>
       </c>
-      <c r="G45" s="177">
-        <f>('Assumptions (3)'!B26*(1+0.07)^2+1500*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="G45" s="159">
+        <f>('Assumptions (VF)'!B26*(1+0.07)^2+1500*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.5610261950748434</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" s="173">
+      <c r="A46" s="155">
         <v>2000</v>
       </c>
-      <c r="B46" s="177">
-        <f>('Assumptions (3)'!B26*(1+0.02)^2+2000*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="B46" s="159">
+        <f>('Assumptions (VF)'!B26*(1+0.02)^2+2000*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.2232087155963294</v>
       </c>
-      <c r="C46" s="177">
-        <f>('Assumptions (3)'!B26*(1+0.03)^2+2000*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="C46" s="159">
+        <f>('Assumptions (VF)'!B26*(1+0.03)^2+2000*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.3113062530178654</v>
       </c>
-      <c r="D46" s="177">
-        <f>('Assumptions (3)'!B26*(1+0.04)^2+2000*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="D46" s="159">
+        <f>('Assumptions (VF)'!B26*(1+0.04)^2+2000*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.4002632786093674</v>
       </c>
-      <c r="E46" s="177">
-        <f>('Assumptions (3)'!B26*(1+0.05)^2+2000*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="E46" s="159">
+        <f>('Assumptions (VF)'!B26*(1+0.05)^2+2000*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.4900797923708353</v>
       </c>
-      <c r="F46" s="177">
-        <f>('Assumptions (3)'!B26*(1+0.06)^2+2000*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="F46" s="159">
+        <f>('Assumptions (VF)'!B26*(1+0.06)^2+2000*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.5807557943022692</v>
       </c>
-      <c r="G46" s="177">
-        <f>('Assumptions (3)'!B26*(1+0.07)^2+2000*1.2*(1-'Assumptions (3)'!F17)-'Assumptions (3)'!F18-'Assumptions (3)'!F21)/('Assumptions (3)'!B7+'Assumptions (3)'!F12)</f>
+      <c r="G46" s="159">
+        <f>('Assumptions (VF)'!B26*(1+0.07)^2+2000*1.2*(1-'Assumptions (VF)'!F17)-'Assumptions (VF)'!F18-'Assumptions (VF)'!F21)/('Assumptions (VF)'!B7+'Assumptions (VF)'!F12)</f>
         <v>4.6722912844036699</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="176" t="s">
+      <c r="A48" s="235" t="s">
         <v>221</v>
       </c>
-      <c r="B48" s="145"/>
-      <c r="C48" s="145"/>
-      <c r="D48" s="145"/>
-      <c r="E48" s="145"/>
-      <c r="F48" s="145"/>
-      <c r="G48" s="145"/>
+      <c r="B48" s="231"/>
+      <c r="C48" s="231"/>
+      <c r="D48" s="231"/>
+      <c r="E48" s="231"/>
+      <c r="F48" s="231"/>
+      <c r="G48" s="231"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" s="167" t="s">
+      <c r="A49" s="151" t="s">
         <v>270</v>
       </c>
-      <c r="B49" s="175">
+      <c r="B49" s="157">
         <v>0.02</v>
       </c>
-      <c r="C49" s="175">
+      <c r="C49" s="157">
         <v>0.03</v>
       </c>
-      <c r="D49" s="167" t="s">
+      <c r="D49" s="151" t="s">
         <v>290</v>
       </c>
-      <c r="E49" s="175">
+      <c r="E49" s="157">
         <v>0.05</v>
       </c>
-      <c r="F49" s="175">
+      <c r="F49" s="157">
         <v>0.06</v>
       </c>
-      <c r="G49" s="175">
+      <c r="G49" s="157">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50" s="173">
+      <c r="A50" s="155">
         <v>0</v>
       </c>
-      <c r="B50" s="174">
-        <f>(B40-('Assumptions (3)'!B23*(1+0.02)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.02)^2/'Assumptions (3)'!B7)</f>
+      <c r="B50" s="156">
+        <f>(B40-('Assumptions (VF)'!B23*(1+0.02)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.02)^2/'Assumptions (VF)'!B7)</f>
         <v>-9.4114559518345409E-2</v>
       </c>
-      <c r="C50" s="174">
-        <f>(C40-('Assumptions (3)'!B23*(1+0.03)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.03)^2/'Assumptions (3)'!B7)</f>
+      <c r="C50" s="156">
+        <f>(C40-('Assumptions (VF)'!B23*(1+0.03)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.03)^2/'Assumptions (VF)'!B7)</f>
         <v>-9.0904227502484169E-2</v>
       </c>
-      <c r="D50" s="174">
-        <f>(D40-('Assumptions (3)'!B23*(1+0.04)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.04)^2/'Assumptions (3)'!B7)</f>
+      <c r="D50" s="156">
+        <f>(D40-('Assumptions (VF)'!B23*(1+0.04)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.04)^2/'Assumptions (VF)'!B7)</f>
         <v>-8.7786055274053421E-2</v>
       </c>
-      <c r="E50" s="174">
-        <f>(E40-('Assumptions (3)'!B23*(1+0.05)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.05)^2/'Assumptions (3)'!B7)</f>
+      <c r="E50" s="156">
+        <f>(E40-('Assumptions (VF)'!B23*(1+0.05)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.05)^2/'Assumptions (VF)'!B7)</f>
         <v>-8.4756548756443464E-2</v>
       </c>
-      <c r="F50" s="174">
-        <f>(F40-('Assumptions (3)'!B23*(1+0.06)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.06)^2/'Assumptions (3)'!B7)</f>
+      <c r="F50" s="156">
+        <f>(F40-('Assumptions (VF)'!B23*(1+0.06)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.06)^2/'Assumptions (VF)'!B7)</f>
         <v>-8.181237790679341E-2</v>
       </c>
-      <c r="G50" s="174">
-        <f>(G40-('Assumptions (3)'!B23*(1+0.07)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.07)^2/'Assumptions (3)'!B7)</f>
+      <c r="G50" s="156">
+        <f>(G40-('Assumptions (VF)'!B23*(1+0.07)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.07)^2/'Assumptions (VF)'!B7)</f>
         <v>-7.8950367561096094E-2</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51" s="173">
+      <c r="A51" s="155">
         <v>250</v>
       </c>
-      <c r="B51" s="174">
-        <f>(B41-('Assumptions (3)'!B23*(1+0.02)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.02)^2/'Assumptions (3)'!B7)</f>
+      <c r="B51" s="156">
+        <f>(B41-('Assumptions (VF)'!B23*(1+0.02)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.02)^2/'Assumptions (VF)'!B7)</f>
         <v>-8.0775561827061845E-2</v>
       </c>
-      <c r="C51" s="174">
-        <f>(C41-('Assumptions (3)'!B23*(1+0.03)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.03)^2/'Assumptions (3)'!B7)</f>
+      <c r="C51" s="156">
+        <f>(C41-('Assumptions (VF)'!B23*(1+0.03)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.03)^2/'Assumptions (VF)'!B7)</f>
         <v>-7.7822982146643349E-2</v>
       </c>
-      <c r="D51" s="174">
-        <f>(D41-('Assumptions (3)'!B23*(1+0.04)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.04)^2/'Assumptions (3)'!B7)</f>
+      <c r="D51" s="156">
+        <f>(D41-('Assumptions (VF)'!B23*(1+0.04)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.04)^2/'Assumptions (VF)'!B7)</f>
         <v>-7.4955162894235178E-2</v>
       </c>
-      <c r="E51" s="174">
-        <f>(E41-('Assumptions (3)'!B23*(1+0.05)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.05)^2/'Assumptions (3)'!B7)</f>
+      <c r="E51" s="156">
+        <f>(E41-('Assumptions (VF)'!B23*(1+0.05)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.05)^2/'Assumptions (VF)'!B7)</f>
         <v>-7.216889052695466E-2</v>
       </c>
-      <c r="F51" s="174">
-        <f>(F41-('Assumptions (3)'!B23*(1+0.06)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.06)^2/'Assumptions (3)'!B7)</f>
+      <c r="F51" s="156">
+        <f>(F41-('Assumptions (VF)'!B23*(1+0.06)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.06)^2/'Assumptions (VF)'!B7)</f>
         <v>-6.9461102365665425E-2</v>
       </c>
-      <c r="G51" s="174">
-        <f>(G41-('Assumptions (3)'!B23*(1+0.07)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.07)^2/'Assumptions (3)'!B7)</f>
+      <c r="G51" s="156">
+        <f>(G41-('Assumptions (VF)'!B23*(1+0.07)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.07)^2/'Assumptions (VF)'!B7)</f>
         <v>-6.6828878175113557E-2</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" s="173">
+      <c r="A52" s="155">
         <v>500</v>
       </c>
-      <c r="B52" s="174">
-        <f>(B42-('Assumptions (3)'!B23*(1+0.02)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.02)^2/'Assumptions (3)'!B7)</f>
+      <c r="B52" s="156">
+        <f>(B42-('Assumptions (VF)'!B23*(1+0.02)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.02)^2/'Assumptions (VF)'!B7)</f>
         <v>-6.7436564135778296E-2</v>
       </c>
-      <c r="C52" s="174">
-        <f>(C42-('Assumptions (3)'!B23*(1+0.03)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.03)^2/'Assumptions (3)'!B7)</f>
+      <c r="C52" s="156">
+        <f>(C42-('Assumptions (VF)'!B23*(1+0.03)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.03)^2/'Assumptions (VF)'!B7)</f>
         <v>-6.474173679080264E-2</v>
       </c>
-      <c r="D52" s="174">
-        <f>(D42-('Assumptions (3)'!B23*(1+0.04)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.04)^2/'Assumptions (3)'!B7)</f>
+      <c r="D52" s="156">
+        <f>(D42-('Assumptions (VF)'!B23*(1+0.04)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.04)^2/'Assumptions (VF)'!B7)</f>
         <v>-6.2124270514416942E-2</v>
       </c>
-      <c r="E52" s="174">
-        <f>(E42-('Assumptions (3)'!B23*(1+0.05)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.05)^2/'Assumptions (3)'!B7)</f>
+      <c r="E52" s="156">
+        <f>(E42-('Assumptions (VF)'!B23*(1+0.05)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.05)^2/'Assumptions (VF)'!B7)</f>
         <v>-5.9581232297465647E-2</v>
       </c>
-      <c r="F52" s="174">
-        <f>(F42-('Assumptions (3)'!B23*(1+0.06)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.06)^2/'Assumptions (3)'!B7)</f>
+      <c r="F52" s="156">
+        <f>(F42-('Assumptions (VF)'!B23*(1+0.06)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.06)^2/'Assumptions (VF)'!B7)</f>
         <v>-5.7109826824537434E-2</v>
       </c>
-      <c r="G52" s="174">
-        <f>(G42-('Assumptions (3)'!B23*(1+0.07)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.07)^2/'Assumptions (3)'!B7)</f>
+      <c r="G52" s="156">
+        <f>(G42-('Assumptions (VF)'!B23*(1+0.07)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.07)^2/'Assumptions (VF)'!B7)</f>
         <v>-5.4707388789130819E-2</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A53" s="173">
+      <c r="A53" s="155">
         <v>750</v>
       </c>
-      <c r="B53" s="174">
-        <f>(B43-('Assumptions (3)'!B23*(1+0.02)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.02)^2/'Assumptions (3)'!B7)</f>
+      <c r="B53" s="156">
+        <f>(B43-('Assumptions (VF)'!B23*(1+0.02)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.02)^2/'Assumptions (VF)'!B7)</f>
         <v>-5.4097566444494635E-2</v>
       </c>
-      <c r="C53" s="174">
-        <f>(C43-('Assumptions (3)'!B23*(1+0.03)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.03)^2/'Assumptions (3)'!B7)</f>
+      <c r="C53" s="156">
+        <f>(C43-('Assumptions (VF)'!B23*(1+0.03)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.03)^2/'Assumptions (VF)'!B7)</f>
         <v>-5.1660491434961917E-2</v>
       </c>
-      <c r="D53" s="174">
-        <f>(D43-('Assumptions (3)'!B23*(1+0.04)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.04)^2/'Assumptions (3)'!B7)</f>
+      <c r="D53" s="156">
+        <f>(D43-('Assumptions (VF)'!B23*(1+0.04)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.04)^2/'Assumptions (VF)'!B7)</f>
         <v>-4.9293378134598491E-2</v>
       </c>
-      <c r="E53" s="174">
-        <f>(E43-('Assumptions (3)'!B23*(1+0.05)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.05)^2/'Assumptions (3)'!B7)</f>
+      <c r="E53" s="156">
+        <f>(E43-('Assumptions (VF)'!B23*(1+0.05)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.05)^2/'Assumptions (VF)'!B7)</f>
         <v>-4.6993574067976836E-2</v>
       </c>
-      <c r="F53" s="174">
-        <f>(F43-('Assumptions (3)'!B23*(1+0.06)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.06)^2/'Assumptions (3)'!B7)</f>
+      <c r="F53" s="156">
+        <f>(F43-('Assumptions (VF)'!B23*(1+0.06)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.06)^2/'Assumptions (VF)'!B7)</f>
         <v>-4.4758551283409442E-2</v>
       </c>
-      <c r="G53" s="174">
-        <f>(G43-('Assumptions (3)'!B23*(1+0.07)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.07)^2/'Assumptions (3)'!B7)</f>
+      <c r="G53" s="156">
+        <f>(G43-('Assumptions (VF)'!B23*(1+0.07)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.07)^2/'Assumptions (VF)'!B7)</f>
         <v>-4.2585899403148275E-2</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54" s="173">
+      <c r="A54" s="155">
         <v>1000</v>
       </c>
-      <c r="B54" s="174">
-        <f>(B44-('Assumptions (3)'!B23*(1+0.02)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.02)^2/'Assumptions (3)'!B7)</f>
+      <c r="B54" s="156">
+        <f>(B44-('Assumptions (VF)'!B23*(1+0.02)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.02)^2/'Assumptions (VF)'!B7)</f>
         <v>-4.0758568753210975E-2</v>
       </c>
-      <c r="C54" s="174">
-        <f>(C44-('Assumptions (3)'!B23*(1+0.03)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.03)^2/'Assumptions (3)'!B7)</f>
+      <c r="C54" s="156">
+        <f>(C44-('Assumptions (VF)'!B23*(1+0.03)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.03)^2/'Assumptions (VF)'!B7)</f>
         <v>-3.8579246079121207E-2</v>
       </c>
-      <c r="D54" s="174">
-        <f>(D44-('Assumptions (3)'!B23*(1+0.04)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.04)^2/'Assumptions (3)'!B7)</f>
+      <c r="D54" s="156">
+        <f>(D44-('Assumptions (VF)'!B23*(1+0.04)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.04)^2/'Assumptions (VF)'!B7)</f>
         <v>-3.6462485754780248E-2</v>
       </c>
-      <c r="E54" s="174">
-        <f>(E44-('Assumptions (3)'!B23*(1+0.05)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.05)^2/'Assumptions (3)'!B7)</f>
+      <c r="E54" s="156">
+        <f>(E44-('Assumptions (VF)'!B23*(1+0.05)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.05)^2/'Assumptions (VF)'!B7)</f>
         <v>-3.4405915838488031E-2</v>
       </c>
-      <c r="F54" s="174">
-        <f>(F44-('Assumptions (3)'!B23*(1+0.06)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.06)^2/'Assumptions (3)'!B7)</f>
+      <c r="F54" s="156">
+        <f>(F44-('Assumptions (VF)'!B23*(1+0.06)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.06)^2/'Assumptions (VF)'!B7)</f>
         <v>-3.2407275742281257E-2</v>
       </c>
-      <c r="G54" s="174">
-        <f>(G44-('Assumptions (3)'!B23*(1+0.07)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.07)^2/'Assumptions (3)'!B7)</f>
+      <c r="G54" s="156">
+        <f>(G44-('Assumptions (VF)'!B23*(1+0.07)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.07)^2/'Assumptions (VF)'!B7)</f>
         <v>-3.0464410017165735E-2</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" s="173">
+      <c r="A55" s="155">
         <v>1500</v>
       </c>
-      <c r="B55" s="172">
-        <f>(B45-('Assumptions (3)'!B23*(1+0.02)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.02)^2/'Assumptions (3)'!B7)</f>
+      <c r="B55" s="154">
+        <f>(B45-('Assumptions (VF)'!B23*(1+0.02)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.02)^2/'Assumptions (VF)'!B7)</f>
         <v>-1.4080573370644079E-2</v>
       </c>
-      <c r="C55" s="172">
-        <f>(C45-('Assumptions (3)'!B23*(1+0.03)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.03)^2/'Assumptions (3)'!B7)</f>
+      <c r="C55" s="154">
+        <f>(C45-('Assumptions (VF)'!B23*(1+0.03)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.03)^2/'Assumptions (VF)'!B7)</f>
         <v>-1.2416755367439778E-2</v>
       </c>
-      <c r="D55" s="172">
-        <f>(D45-('Assumptions (3)'!B23*(1+0.04)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.04)^2/'Assumptions (3)'!B7)</f>
+      <c r="D55" s="154">
+        <f>(D45-('Assumptions (VF)'!B23*(1+0.04)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.04)^2/'Assumptions (VF)'!B7)</f>
         <v>-1.0800700995143766E-2</v>
       </c>
-      <c r="E55" s="172">
-        <f>(E45-('Assumptions (3)'!B23*(1+0.05)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.05)^2/'Assumptions (3)'!B7)</f>
+      <c r="E55" s="154">
+        <f>(E45-('Assumptions (VF)'!B23*(1+0.05)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.05)^2/'Assumptions (VF)'!B7)</f>
         <v>-9.2305993795104135E-3</v>
       </c>
-      <c r="F55" s="172">
-        <f>(F45-('Assumptions (3)'!B23*(1+0.06)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.06)^2/'Assumptions (3)'!B7)</f>
+      <c r="F55" s="154">
+        <f>(F45-('Assumptions (VF)'!B23*(1+0.06)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.06)^2/'Assumptions (VF)'!B7)</f>
         <v>-7.7047246600252754E-3</v>
       </c>
-      <c r="G55" s="172">
-        <f>(G45-('Assumptions (3)'!B23*(1+0.07)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.07)^2/'Assumptions (3)'!B7)</f>
+      <c r="G55" s="154">
+        <f>(G45-('Assumptions (VF)'!B23*(1+0.07)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.07)^2/'Assumptions (VF)'!B7)</f>
         <v>-6.2214312452006509E-3</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56" s="173">
+      <c r="A56" s="155">
         <v>2000</v>
       </c>
-      <c r="B56" s="172">
-        <f>(B46-('Assumptions (3)'!B23*(1+0.02)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.02)^2/'Assumptions (3)'!B7)</f>
+      <c r="B56" s="154">
+        <f>(B46-('Assumptions (VF)'!B23*(1+0.02)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.02)^2/'Assumptions (VF)'!B7)</f>
         <v>1.2597422011923031E-2</v>
       </c>
-      <c r="C56" s="172">
-        <f>(C46-('Assumptions (3)'!B23*(1+0.03)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.03)^2/'Assumptions (3)'!B7)</f>
+      <c r="C56" s="154">
+        <f>(C46-('Assumptions (VF)'!B23*(1+0.03)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.03)^2/'Assumptions (VF)'!B7)</f>
         <v>1.3745735344241648E-2</v>
       </c>
-      <c r="D56" s="172">
-        <f>(D46-('Assumptions (3)'!B23*(1+0.04)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.04)^2/'Assumptions (3)'!B7)</f>
+      <c r="D56" s="154">
+        <f>(D46-('Assumptions (VF)'!B23*(1+0.04)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.04)^2/'Assumptions (VF)'!B7)</f>
         <v>1.4861083764492515E-2</v>
       </c>
-      <c r="E56" s="172">
-        <f>(E46-('Assumptions (3)'!B23*(1+0.05)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.05)^2/'Assumptions (3)'!B7)</f>
+      <c r="E56" s="154">
+        <f>(E46-('Assumptions (VF)'!B23*(1+0.05)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.05)^2/'Assumptions (VF)'!B7)</f>
         <v>1.5944717079467201E-2</v>
       </c>
-      <c r="F56" s="172">
-        <f>(F46-('Assumptions (3)'!B23*(1+0.06)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.06)^2/'Assumptions (3)'!B7)</f>
+      <c r="F56" s="154">
+        <f>(F46-('Assumptions (VF)'!B23*(1+0.06)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.06)^2/'Assumptions (VF)'!B7)</f>
         <v>1.6997826422230508E-2</v>
       </c>
-      <c r="G56" s="172">
-        <f>(G46-('Assumptions (3)'!B23*(1+0.07)^2/'Assumptions (3)'!B7))/('Assumptions (3)'!B23*(1+0.07)^2/'Assumptions (3)'!B7)</f>
+      <c r="G56" s="154">
+        <f>(G46-('Assumptions (VF)'!B23*(1+0.07)^2/'Assumptions (VF)'!B7))/('Assumptions (VF)'!B23*(1+0.07)^2/'Assumptions (VF)'!B7)</f>
         <v>1.8021547526764433E-2</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A58" s="146" t="s">
+      <c r="A58" s="230" t="s">
         <v>277</v>
       </c>
-      <c r="B58" s="145"/>
-      <c r="C58" s="145"/>
-      <c r="D58" s="145"/>
-      <c r="E58" s="145"/>
-      <c r="F58" s="145"/>
-      <c r="G58" s="145"/>
+      <c r="B58" s="231"/>
+      <c r="C58" s="231"/>
+      <c r="D58" s="231"/>
+      <c r="E58" s="231"/>
+      <c r="F58" s="231"/>
+      <c r="G58" s="231"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -8148,38 +8169,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="217" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
-      <c r="M1" s="131"/>
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="217"/>
+      <c r="J1" s="217"/>
+      <c r="K1" s="217"/>
+      <c r="L1" s="217"/>
+      <c r="M1" s="217"/>
     </row>
     <row r="2" spans="1:13" ht="21" x14ac:dyDescent="0.2">
-      <c r="A2" s="132" t="s">
+      <c r="A2" s="218" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
+      <c r="B2" s="218"/>
+      <c r="C2" s="218"/>
+      <c r="D2" s="218"/>
+      <c r="E2" s="218"/>
+      <c r="F2" s="218"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="218"/>
+      <c r="I2" s="218"/>
+      <c r="J2" s="218"/>
+      <c r="K2" s="218"/>
+      <c r="L2" s="218"/>
+      <c r="M2" s="218"/>
     </row>
     <row r="4" spans="1:13" s="101" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="B4" s="101" t="s">
@@ -8263,172 +8284,173 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9333DECA-349A-A844-9929-BB338FE00309}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="44" style="144" customWidth="1"/>
-    <col min="2" max="2" width="18" style="144" customWidth="1"/>
-    <col min="3" max="3" width="16" style="144" customWidth="1"/>
-    <col min="4" max="4" width="38" style="144" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="144"/>
+    <col min="1" max="1" width="44" style="131" customWidth="1"/>
+    <col min="2" max="2" width="18" style="131" customWidth="1"/>
+    <col min="3" max="3" width="16" style="131" customWidth="1"/>
+    <col min="4" max="4" width="38" style="131" customWidth="1"/>
+    <col min="5" max="16384" width="8.83203125" style="131"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="171" t="s">
+    <row r="1" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="233" t="s">
         <v>222</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-    </row>
-    <row r="2" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="170" t="s">
+      <c r="B1" s="231"/>
+      <c r="C1" s="231"/>
+      <c r="D1" s="231"/>
+    </row>
+    <row r="2" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="232" t="s">
         <v>223</v>
       </c>
-      <c r="B2" s="145"/>
-      <c r="C2" s="145"/>
-      <c r="D2" s="145"/>
-    </row>
-    <row r="3" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="189" t="s">
+      <c r="B2" s="231"/>
+      <c r="C2" s="231"/>
+      <c r="D2" s="231"/>
+    </row>
+    <row r="3" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="158" t="s">
         <v>224</v>
       </c>
-      <c r="B4" s="189" t="s">
+      <c r="B4" s="158" t="s">
         <v>225</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="158" t="s">
         <v>226</v>
       </c>
-      <c r="D4" s="189" t="s">
+      <c r="D4" s="158" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="159" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="143" t="s">
         <v>228</v>
       </c>
-      <c r="B5" s="157">
+      <c r="B5" s="141">
         <v>58893</v>
       </c>
-      <c r="C5" s="158">
+      <c r="C5" s="142">
         <f>B5/B9</f>
         <v>0.45302307692307692</v>
       </c>
-      <c r="D5" s="151" t="s">
+      <c r="D5" s="135" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="155" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="139" t="s">
         <v>230</v>
       </c>
-      <c r="B6" s="154">
+      <c r="B6" s="138">
         <v>60895</v>
       </c>
-      <c r="C6" s="160">
+      <c r="C6" s="144">
         <f>B6/B9</f>
         <v>0.46842307692307694</v>
       </c>
-      <c r="D6" s="148" t="s">
+      <c r="D6" s="132" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="159" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="143" t="s">
         <v>232</v>
       </c>
-      <c r="B7" s="157">
-        <v>3500</v>
-      </c>
-      <c r="C7" s="158">
+      <c r="B7" s="141">
+        <v>5000</v>
+      </c>
+      <c r="C7" s="142">
         <f>B7/B9</f>
-        <v>2.6923076923076925E-2</v>
-      </c>
-      <c r="D7" s="151" t="s">
+        <v>3.8461538461538464E-2</v>
+      </c>
+      <c r="D7" s="135" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="155" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="139" t="s">
         <v>233</v>
       </c>
-      <c r="B8" s="149">
+      <c r="B8" s="133">
         <f>B9-B5-B6-B7</f>
-        <v>6712</v>
-      </c>
-      <c r="C8" s="160">
+        <v>5212</v>
+      </c>
+      <c r="C8" s="144">
         <f>B8/B9</f>
-        <v>5.163076923076923E-2</v>
-      </c>
-      <c r="D8" s="148" t="s">
+        <v>4.0092307692307691E-2</v>
+      </c>
+      <c r="D8" s="132" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="153" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="137" t="s">
         <v>235</v>
       </c>
-      <c r="B9" s="157">
+      <c r="B9" s="141">
         <v>130000</v>
       </c>
-      <c r="C9" s="158">
+      <c r="C9" s="142">
         <f>SUM(C5:C8)</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="D9" s="135" t="s">
+        <v>236</v>
+      </c>
+      <c r="E9" s="214"/>
+    </row>
+    <row r="10" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="153" t="s">
+        <v>237</v>
+      </c>
+      <c r="B11" s="152"/>
+      <c r="C11" s="152"/>
+      <c r="D11" s="152"/>
+    </row>
+    <row r="12" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="151" t="s">
+        <v>238</v>
+      </c>
+      <c r="B12" s="151" t="s">
+        <v>281</v>
+      </c>
+      <c r="C12" s="151" t="s">
+        <v>282</v>
+      </c>
+      <c r="D12" s="151" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="143" t="s">
+        <v>242</v>
+      </c>
+      <c r="B13" s="172">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="C13" s="172">
         <v>1</v>
       </c>
-      <c r="D9" s="151" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="169" t="s">
-        <v>237</v>
-      </c>
-      <c r="B11" s="168"/>
-      <c r="C11" s="168"/>
-      <c r="D11" s="168"/>
-    </row>
-    <row r="12" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="167" t="s">
-        <v>238</v>
-      </c>
-      <c r="B12" s="167" t="s">
-        <v>281</v>
-      </c>
-      <c r="C12" s="167" t="s">
-        <v>282</v>
-      </c>
-      <c r="D12" s="167" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="159" t="s">
-        <v>242</v>
-      </c>
-      <c r="B13" s="191">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="C13" s="191">
-        <v>1</v>
-      </c>
-      <c r="D13" s="191">
+      <c r="D13" s="172">
         <f>C13-B13</f>
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="155" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="139" t="s">
         <v>243</v>
       </c>
-      <c r="B14" s="190">
+      <c r="B14" s="171">
         <v>0.45</v>
       </c>
-      <c r="C14" s="190">
+      <c r="C14" s="171">
         <v>0</v>
       </c>
-      <c r="D14" s="190">
+      <c r="D14" s="171">
         <f>C14-B14</f>
         <v>-0.45</v>
       </c>
@@ -8451,87 +8473,87 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="236" t="s">
         <v>313</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="192"/>
-      <c r="H1" s="192"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="192"/>
-      <c r="K1" s="192"/>
-      <c r="L1" s="192"/>
-      <c r="M1" s="192"/>
-      <c r="N1" s="192"/>
-      <c r="O1" s="192"/>
-      <c r="P1" s="192"/>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="192"/>
-      <c r="T1" s="192"/>
-      <c r="U1" s="192"/>
-      <c r="V1" s="192"/>
-      <c r="W1" s="192"/>
-      <c r="X1" s="192"/>
-      <c r="Y1" s="192"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="236"/>
+      <c r="I1" s="236"/>
+      <c r="J1" s="236"/>
+      <c r="K1" s="236"/>
+      <c r="L1" s="236"/>
+      <c r="M1" s="236"/>
+      <c r="N1" s="236"/>
+      <c r="O1" s="236"/>
+      <c r="P1" s="236"/>
+      <c r="Q1" s="236"/>
+      <c r="R1" s="236"/>
+      <c r="S1" s="236"/>
+      <c r="T1" s="236"/>
+      <c r="U1" s="236"/>
+      <c r="V1" s="236"/>
+      <c r="W1" s="236"/>
+      <c r="X1" s="236"/>
+      <c r="Y1" s="236"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="192"/>
-      <c r="B2" s="192"/>
-      <c r="C2" s="192"/>
-      <c r="D2" s="192"/>
-      <c r="E2" s="192"/>
-      <c r="F2" s="192"/>
-      <c r="G2" s="192"/>
-      <c r="H2" s="192"/>
-      <c r="I2" s="192"/>
-      <c r="J2" s="192"/>
-      <c r="K2" s="192"/>
-      <c r="L2" s="192"/>
-      <c r="M2" s="192"/>
-      <c r="N2" s="192"/>
-      <c r="O2" s="192"/>
-      <c r="P2" s="192"/>
-      <c r="Q2" s="192"/>
-      <c r="R2" s="192"/>
-      <c r="S2" s="192"/>
-      <c r="T2" s="192"/>
-      <c r="U2" s="192"/>
-      <c r="V2" s="192"/>
-      <c r="W2" s="192"/>
-      <c r="X2" s="192"/>
-      <c r="Y2" s="192"/>
+      <c r="A2" s="236"/>
+      <c r="B2" s="236"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
+      <c r="L2" s="236"/>
+      <c r="M2" s="236"/>
+      <c r="N2" s="236"/>
+      <c r="O2" s="236"/>
+      <c r="P2" s="236"/>
+      <c r="Q2" s="236"/>
+      <c r="R2" s="236"/>
+      <c r="S2" s="236"/>
+      <c r="T2" s="236"/>
+      <c r="U2" s="236"/>
+      <c r="V2" s="236"/>
+      <c r="W2" s="236"/>
+      <c r="X2" s="236"/>
+      <c r="Y2" s="236"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="192"/>
-      <c r="B3" s="192"/>
-      <c r="C3" s="192"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="192"/>
-      <c r="F3" s="192"/>
-      <c r="G3" s="192"/>
-      <c r="H3" s="192"/>
-      <c r="I3" s="192"/>
-      <c r="J3" s="192"/>
-      <c r="K3" s="192"/>
-      <c r="L3" s="192"/>
-      <c r="M3" s="192"/>
-      <c r="N3" s="192"/>
-      <c r="O3" s="192"/>
-      <c r="P3" s="192"/>
-      <c r="Q3" s="192"/>
-      <c r="R3" s="192"/>
-      <c r="S3" s="192"/>
-      <c r="T3" s="192"/>
-      <c r="U3" s="192"/>
-      <c r="V3" s="192"/>
-      <c r="W3" s="192"/>
-      <c r="X3" s="192"/>
-      <c r="Y3" s="192"/>
+      <c r="A3" s="236"/>
+      <c r="B3" s="236"/>
+      <c r="C3" s="236"/>
+      <c r="D3" s="236"/>
+      <c r="E3" s="236"/>
+      <c r="F3" s="236"/>
+      <c r="G3" s="236"/>
+      <c r="H3" s="236"/>
+      <c r="I3" s="236"/>
+      <c r="J3" s="236"/>
+      <c r="K3" s="236"/>
+      <c r="L3" s="236"/>
+      <c r="M3" s="236"/>
+      <c r="N3" s="236"/>
+      <c r="O3" s="236"/>
+      <c r="P3" s="236"/>
+      <c r="Q3" s="236"/>
+      <c r="R3" s="236"/>
+      <c r="S3" s="236"/>
+      <c r="T3" s="236"/>
+      <c r="U3" s="236"/>
+      <c r="V3" s="236"/>
+      <c r="W3" s="236"/>
+      <c r="X3" s="236"/>
+      <c r="Y3" s="236"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8554,1049 +8576,1061 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="222" t="s">
+      <c r="A1" s="239" t="s">
         <v>368</v>
       </c>
-      <c r="B1" s="222"/>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
-      <c r="F1" s="222"/>
-      <c r="G1" s="222"/>
-      <c r="H1" s="222"/>
-      <c r="I1" s="222"/>
+      <c r="B1" s="239"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="239"/>
+      <c r="H1" s="239"/>
+      <c r="I1" s="239"/>
     </row>
     <row r="2" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="221" t="s">
+      <c r="A2" s="240" t="s">
         <v>367</v>
       </c>
-      <c r="B2" s="221"/>
-      <c r="C2" s="221"/>
-      <c r="D2" s="221"/>
-      <c r="E2" s="221"/>
-      <c r="F2" s="221"/>
-      <c r="G2" s="221"/>
-      <c r="H2" s="221"/>
-      <c r="I2" s="221"/>
+      <c r="B2" s="240"/>
+      <c r="C2" s="240"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="240"/>
+      <c r="H2" s="240"/>
+      <c r="I2" s="240"/>
     </row>
     <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="220" t="s">
+      <c r="B3" s="241" t="s">
         <v>366</v>
       </c>
-      <c r="C3" s="220"/>
-      <c r="D3" s="220"/>
-      <c r="E3" s="219" t="s">
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="194" t="s">
         <v>365</v>
       </c>
-      <c r="F3" s="218" t="s">
+      <c r="F3" s="242" t="s">
         <v>364</v>
       </c>
-      <c r="G3" s="218"/>
-      <c r="H3" s="218"/>
-      <c r="I3" s="218"/>
+      <c r="G3" s="242"/>
+      <c r="H3" s="242"/>
+      <c r="I3" s="242"/>
     </row>
     <row r="4" spans="1:9" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="217" t="s">
+      <c r="A4" s="193" t="s">
         <v>363</v>
       </c>
-      <c r="B4" s="216" t="s">
+      <c r="B4" s="192" t="s">
         <v>362</v>
       </c>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="192" t="s">
         <v>361</v>
       </c>
-      <c r="D4" s="216" t="s">
+      <c r="D4" s="192" t="s">
         <v>360</v>
       </c>
-      <c r="E4" s="216" t="s">
+      <c r="E4" s="192" t="s">
         <v>359</v>
       </c>
-      <c r="F4" s="216" t="s">
+      <c r="F4" s="192" t="s">
         <v>358</v>
       </c>
-      <c r="G4" s="216" t="s">
+      <c r="G4" s="192" t="s">
         <v>357</v>
       </c>
-      <c r="H4" s="216" t="s">
+      <c r="H4" s="192" t="s">
         <v>356</v>
       </c>
-      <c r="I4" s="216" t="s">
+      <c r="I4" s="192" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="208" t="s">
+      <c r="A5" s="243" t="s">
         <v>354</v>
       </c>
-      <c r="B5" s="208"/>
-      <c r="C5" s="208"/>
-      <c r="D5" s="208"/>
-      <c r="E5" s="208"/>
-      <c r="F5" s="208"/>
-      <c r="G5" s="208"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="208"/>
+      <c r="B5" s="243"/>
+      <c r="C5" s="243"/>
+      <c r="D5" s="243"/>
+      <c r="E5" s="243"/>
+      <c r="F5" s="243"/>
+      <c r="G5" s="243"/>
+      <c r="H5" s="243"/>
+      <c r="I5" s="243"/>
     </row>
     <row r="6" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="212" t="s">
+      <c r="A6" s="188" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="214">
+      <c r="B6" s="190">
         <v>115846</v>
       </c>
-      <c r="C6" s="214">
+      <c r="C6" s="190">
         <v>115302</v>
       </c>
-      <c r="D6" s="214">
+      <c r="D6" s="190">
         <v>120550</v>
       </c>
-      <c r="E6" s="214">
+      <c r="E6" s="190">
         <v>127079</v>
       </c>
-      <c r="F6" s="214">
+      <c r="F6" s="190">
         <v>131620</v>
       </c>
-      <c r="G6" s="214">
+      <c r="G6" s="190">
         <v>125980</v>
       </c>
-      <c r="H6" s="214">
+      <c r="H6" s="190">
         <v>126034</v>
       </c>
-      <c r="I6" s="214">
+      <c r="I6" s="190">
         <v>130863</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="210" t="s">
+      <c r="A7" s="186" t="s">
         <v>353</v>
       </c>
-      <c r="B7" s="214">
+      <c r="B7" s="190">
         <v>14688</v>
       </c>
-      <c r="C7" s="214">
+      <c r="C7" s="190">
         <v>13160</v>
       </c>
-      <c r="D7" s="214">
+      <c r="D7" s="190">
         <v>16303</v>
       </c>
-      <c r="E7" s="214">
+      <c r="E7" s="190">
         <v>18496</v>
       </c>
-      <c r="F7" s="214">
+      <c r="F7" s="190">
         <v>33060</v>
       </c>
-      <c r="G7" s="214">
+      <c r="G7" s="190">
         <v>30496</v>
       </c>
-      <c r="H7" s="214">
+      <c r="H7" s="190">
         <v>26978</v>
       </c>
-      <c r="I7" s="214">
+      <c r="I7" s="190">
         <v>30015</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="212" t="s">
+      <c r="A8" s="188" t="s">
         <v>352</v>
       </c>
-      <c r="B8" s="215">
+      <c r="B8" s="191">
         <v>0.28100000000000003</v>
       </c>
-      <c r="C8" s="215">
+      <c r="C8" s="191">
         <v>0.28699999999999998</v>
       </c>
-      <c r="D8" s="215">
+      <c r="D8" s="191">
         <v>0.29899999999999999</v>
       </c>
-      <c r="E8" s="215">
+      <c r="E8" s="191">
         <v>0.30499999999999999</v>
       </c>
-      <c r="F8" s="215">
+      <c r="F8" s="191">
         <v>0.36099999999999999</v>
       </c>
-      <c r="G8" s="215">
+      <c r="G8" s="191">
         <v>0.35399999999999998</v>
       </c>
-      <c r="H8" s="215">
+      <c r="H8" s="191">
         <v>0.36699999999999999</v>
       </c>
-      <c r="I8" s="215">
+      <c r="I8" s="191">
         <v>0.218</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="205" t="s">
+      <c r="A9" s="182" t="s">
         <v>351</v>
       </c>
-      <c r="B9" s="213">
-        <f>B7*(1-B8)</f>
+      <c r="B9" s="189">
+        <f t="shared" ref="B9:I9" si="0">B7*(1-B8)</f>
         <v>10560.672</v>
       </c>
-      <c r="C9" s="213">
-        <f>C7*(1-C8)</f>
+      <c r="C9" s="189">
+        <f t="shared" si="0"/>
         <v>9383.0800000000017</v>
       </c>
-      <c r="D9" s="213">
-        <f>D7*(1-D8)</f>
+      <c r="D9" s="189">
+        <f t="shared" si="0"/>
         <v>11428.403</v>
       </c>
-      <c r="E9" s="213">
-        <f>E7*(1-E8)</f>
+      <c r="E9" s="189">
+        <f t="shared" si="0"/>
         <v>12854.720000000001</v>
       </c>
-      <c r="F9" s="213">
-        <f>F7*(1-F8)</f>
+      <c r="F9" s="189">
+        <f t="shared" si="0"/>
         <v>21125.34</v>
       </c>
-      <c r="G9" s="213">
-        <f>G7*(1-G8)</f>
+      <c r="G9" s="189">
+        <f t="shared" si="0"/>
         <v>19700.416000000001</v>
       </c>
-      <c r="H9" s="213">
-        <f>H7*(1-H8)</f>
+      <c r="H9" s="189">
+        <f t="shared" si="0"/>
         <v>17077.074000000001</v>
       </c>
-      <c r="I9" s="213">
-        <f>I7*(1-I8)</f>
+      <c r="I9" s="189">
+        <f t="shared" si="0"/>
         <v>23471.73</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="208" t="s">
+      <c r="A10" s="243" t="s">
         <v>350</v>
       </c>
-      <c r="B10" s="208"/>
-      <c r="C10" s="208"/>
-      <c r="D10" s="208"/>
-      <c r="E10" s="208"/>
-      <c r="F10" s="208"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="208"/>
-      <c r="I10" s="208"/>
+      <c r="B10" s="243"/>
+      <c r="C10" s="243"/>
+      <c r="D10" s="243"/>
+      <c r="E10" s="243"/>
+      <c r="F10" s="243"/>
+      <c r="G10" s="243"/>
+      <c r="H10" s="243"/>
+      <c r="I10" s="243"/>
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="210" t="s">
+      <c r="A11" s="186" t="s">
         <v>349</v>
       </c>
-      <c r="B11" s="214">
+      <c r="B11" s="190">
         <v>52814</v>
       </c>
-      <c r="C11" s="214">
+      <c r="C11" s="190">
         <v>54059</v>
       </c>
-      <c r="D11" s="214">
+      <c r="D11" s="190">
         <v>89850</v>
       </c>
-      <c r="E11" s="214">
+      <c r="E11" s="190">
         <v>110536</v>
       </c>
-      <c r="F11" s="214">
+      <c r="F11" s="190">
         <v>109652</v>
       </c>
-      <c r="G11" s="214">
+      <c r="G11" s="190">
         <v>108209</v>
       </c>
-      <c r="H11" s="214">
+      <c r="H11" s="190">
         <v>117068</v>
       </c>
-      <c r="I11" s="214">
+      <c r="I11" s="190">
         <v>116073</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="212" t="s">
+      <c r="A12" s="188" t="s">
         <v>348</v>
       </c>
-      <c r="B12" s="214">
+      <c r="B12" s="190">
         <v>38569</v>
       </c>
-      <c r="C12" s="214">
+      <c r="C12" s="190">
         <v>31974</v>
       </c>
-      <c r="D12" s="214">
+      <c r="D12" s="190">
         <v>24232</v>
       </c>
-      <c r="E12" s="214">
+      <c r="E12" s="190">
         <v>12523</v>
       </c>
-      <c r="F12" s="214">
+      <c r="F12" s="190">
         <v>17842</v>
       </c>
-      <c r="G12" s="214">
+      <c r="G12" s="190">
         <v>21961</v>
       </c>
-      <c r="H12" s="214">
+      <c r="H12" s="190">
         <v>24060</v>
       </c>
-      <c r="I12" s="214">
+      <c r="I12" s="190">
         <v>25268</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="210" t="s">
+      <c r="A13" s="186" t="s">
         <v>347</v>
       </c>
-      <c r="B13" s="214">
+      <c r="B13" s="190">
         <v>38416</v>
       </c>
-      <c r="C13" s="214">
+      <c r="C13" s="190">
         <v>37916</v>
       </c>
-      <c r="D13" s="214">
+      <c r="D13" s="190">
         <v>37378</v>
       </c>
-      <c r="E13" s="214">
+      <c r="E13" s="190">
         <v>107447</v>
       </c>
-      <c r="F13" s="214">
+      <c r="F13" s="190">
         <v>108249</v>
       </c>
-      <c r="G13" s="214">
+      <c r="G13" s="190">
         <v>107219</v>
       </c>
-      <c r="H13" s="214">
+      <c r="H13" s="190">
         <v>105576</v>
       </c>
-      <c r="I13" s="214">
+      <c r="I13" s="190">
         <v>104380</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="205" t="s">
+      <c r="A14" s="182" t="s">
         <v>346</v>
       </c>
-      <c r="B14" s="213">
-        <f>B11+B12</f>
+      <c r="B14" s="189">
+        <f t="shared" ref="B14:I14" si="1">B11+B12</f>
         <v>91383</v>
       </c>
-      <c r="C14" s="213">
-        <f>C11+C12</f>
+      <c r="C14" s="189">
+        <f t="shared" si="1"/>
         <v>86033</v>
       </c>
-      <c r="D14" s="213">
-        <f>D11+D12</f>
+      <c r="D14" s="189">
+        <f t="shared" si="1"/>
         <v>114082</v>
       </c>
-      <c r="E14" s="213">
-        <f>E11+E12</f>
+      <c r="E14" s="189">
+        <f t="shared" si="1"/>
         <v>123059</v>
       </c>
-      <c r="F14" s="213">
-        <f>F11+F12</f>
+      <c r="F14" s="189">
+        <f t="shared" si="1"/>
         <v>127494</v>
       </c>
-      <c r="G14" s="213">
-        <f>G11+G12</f>
+      <c r="G14" s="189">
+        <f t="shared" si="1"/>
         <v>130170</v>
       </c>
-      <c r="H14" s="213">
-        <f>H11+H12</f>
+      <c r="H14" s="189">
+        <f t="shared" si="1"/>
         <v>141128</v>
       </c>
-      <c r="I14" s="213">
-        <f>I11+I12</f>
+      <c r="I14" s="189">
+        <f t="shared" si="1"/>
         <v>141341</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="205" t="s">
+      <c r="A15" s="182" t="s">
         <v>345</v>
       </c>
-      <c r="B15" s="213">
+      <c r="B15" s="189">
         <f>B14</f>
         <v>91383</v>
       </c>
-      <c r="C15" s="213">
-        <f>(C14+B14)/2</f>
+      <c r="C15" s="189">
+        <f t="shared" ref="C15:I15" si="2">(C14+B14)/2</f>
         <v>88708</v>
       </c>
-      <c r="D15" s="213">
-        <f>(D14+C14)/2</f>
+      <c r="D15" s="189">
+        <f t="shared" si="2"/>
         <v>100057.5</v>
       </c>
-      <c r="E15" s="213">
-        <f>(E14+D14)/2</f>
+      <c r="E15" s="189">
+        <f t="shared" si="2"/>
         <v>118570.5</v>
       </c>
-      <c r="F15" s="213">
-        <f>(F14+E14)/2</f>
+      <c r="F15" s="189">
+        <f t="shared" si="2"/>
         <v>125276.5</v>
       </c>
-      <c r="G15" s="213">
-        <f>(G14+F14)/2</f>
+      <c r="G15" s="189">
+        <f t="shared" si="2"/>
         <v>128832</v>
       </c>
-      <c r="H15" s="213">
-        <f>(H14+G14)/2</f>
+      <c r="H15" s="189">
+        <f t="shared" si="2"/>
         <v>135649</v>
       </c>
-      <c r="I15" s="213">
-        <f>(I14+H14)/2</f>
+      <c r="I15" s="189">
+        <f t="shared" si="2"/>
         <v>141234.5</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="208" t="s">
+      <c r="A16" s="243" t="s">
         <v>344</v>
       </c>
-      <c r="B16" s="208"/>
-      <c r="C16" s="208"/>
-      <c r="D16" s="208"/>
-      <c r="E16" s="208"/>
-      <c r="F16" s="208"/>
-      <c r="G16" s="208"/>
-      <c r="H16" s="208"/>
-      <c r="I16" s="208"/>
+      <c r="B16" s="243"/>
+      <c r="C16" s="243"/>
+      <c r="D16" s="243"/>
+      <c r="E16" s="243"/>
+      <c r="F16" s="243"/>
+      <c r="G16" s="243"/>
+      <c r="H16" s="243"/>
+      <c r="I16" s="243"/>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="210" t="s">
+      <c r="A17" s="186" t="s">
         <v>343</v>
       </c>
-      <c r="B17" s="209">
+      <c r="B17" s="185">
         <v>1.8800000000000001E-2</v>
       </c>
-      <c r="C17" s="209">
+      <c r="C17" s="185">
         <v>1.7600000000000001E-2</v>
       </c>
-      <c r="D17" s="209">
+      <c r="D17" s="185">
         <v>2.35E-2</v>
       </c>
-      <c r="E17" s="209">
+      <c r="E17" s="185">
         <v>2.5399999999999999E-2</v>
       </c>
-      <c r="F17" s="209">
+      <c r="F17" s="185">
         <v>2.2100000000000002E-2</v>
       </c>
-      <c r="G17" s="209">
+      <c r="G17" s="185">
         <v>2.4500000000000001E-2</v>
       </c>
-      <c r="H17" s="209">
+      <c r="H17" s="185">
         <v>2.3300000000000001E-2</v>
       </c>
-      <c r="I17" s="209">
+      <c r="I17" s="185">
         <v>2.9100000000000001E-2</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="212" t="s">
+      <c r="A18" s="188" t="s">
         <v>342</v>
       </c>
-      <c r="B18" s="209">
+      <c r="B18" s="185">
         <v>5.5E-2</v>
       </c>
-      <c r="C18" s="209">
+      <c r="C18" s="185">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="D18" s="209">
+      <c r="D18" s="185">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="E18" s="209">
+      <c r="E18" s="185">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="F18" s="209">
+      <c r="F18" s="185">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="G18" s="209">
+      <c r="G18" s="185">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="H18" s="209">
+      <c r="H18" s="185">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="I18" s="209">
+      <c r="I18" s="185">
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="210" t="s">
+      <c r="A19" s="186" t="s">
         <v>341</v>
       </c>
-      <c r="B19" s="211">
+      <c r="B19" s="187">
         <v>0.52</v>
       </c>
-      <c r="C19" s="211">
+      <c r="C19" s="187">
         <v>0.5</v>
       </c>
-      <c r="D19" s="211">
+      <c r="D19" s="187">
         <v>0.48</v>
       </c>
-      <c r="E19" s="211">
+      <c r="E19" s="187">
         <v>0.5</v>
       </c>
-      <c r="F19" s="211">
+      <c r="F19" s="187">
         <v>0.55000000000000004</v>
       </c>
-      <c r="G19" s="211">
+      <c r="G19" s="187">
         <v>0.56999999999999995</v>
       </c>
-      <c r="H19" s="211">
+      <c r="H19" s="187">
         <v>0.57999999999999996</v>
       </c>
-      <c r="I19" s="211">
+      <c r="I19" s="187">
         <v>0.6</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="205" t="s">
+      <c r="A20" s="182" t="s">
         <v>340</v>
       </c>
-      <c r="B20" s="204">
-        <f>B17+B19*B18</f>
+      <c r="B20" s="181">
+        <f t="shared" ref="B20:I20" si="3">B17+B19*B18</f>
         <v>4.7399999999999998E-2</v>
       </c>
-      <c r="C20" s="204">
-        <f>C17+C19*C18</f>
+      <c r="C20" s="181">
+        <f t="shared" si="3"/>
         <v>4.5600000000000002E-2</v>
       </c>
-      <c r="D20" s="204">
-        <f>D17+D19*D18</f>
+      <c r="D20" s="181">
+        <f t="shared" si="3"/>
         <v>4.9419999999999999E-2</v>
       </c>
-      <c r="E20" s="204">
-        <f>E17+E19*E18</f>
+      <c r="E20" s="181">
+        <f t="shared" si="3"/>
         <v>5.2400000000000002E-2</v>
       </c>
-      <c r="F20" s="204">
-        <f>F17+F19*F18</f>
+      <c r="F20" s="181">
+        <f t="shared" si="3"/>
         <v>5.1250000000000004E-2</v>
       </c>
-      <c r="G20" s="204">
-        <f>G17+G19*G18</f>
+      <c r="G20" s="181">
+        <f t="shared" si="3"/>
         <v>5.4139999999999994E-2</v>
       </c>
-      <c r="H20" s="204">
-        <f>H17+H19*H18</f>
+      <c r="H20" s="181">
+        <f t="shared" si="3"/>
         <v>5.2879999999999996E-2</v>
       </c>
-      <c r="I20" s="204">
-        <f>I17+I19*I18</f>
+      <c r="I20" s="181">
+        <f t="shared" si="3"/>
         <v>5.9699999999999996E-2</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="210" t="s">
+      <c r="A21" s="186" t="s">
         <v>339</v>
       </c>
-      <c r="B21" s="209">
+      <c r="B21" s="185">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="C21" s="209">
+      <c r="C21" s="185">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="D21" s="209">
+      <c r="D21" s="185">
         <v>4.7E-2</v>
       </c>
-      <c r="E21" s="209">
+      <c r="E21" s="185">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="F21" s="209">
+      <c r="F21" s="185">
         <v>4.1500000000000002E-2</v>
       </c>
-      <c r="G21" s="209">
+      <c r="G21" s="185">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="H21" s="209">
+      <c r="H21" s="185">
         <v>4.0800000000000003E-2</v>
       </c>
-      <c r="I21" s="209">
+      <c r="I21" s="185">
         <v>4.1500000000000002E-2</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="205" t="s">
+      <c r="A22" s="182" t="s">
         <v>338</v>
       </c>
-      <c r="B22" s="204">
-        <f>B21*(1-B8)</f>
+      <c r="B22" s="181">
+        <f t="shared" ref="B22:I22" si="4">B21*(1-B8)</f>
         <v>3.6668999999999993E-2</v>
       </c>
-      <c r="C22" s="204">
-        <f>C21*(1-C8)</f>
+      <c r="C22" s="181">
+        <f t="shared" si="4"/>
         <v>3.4937000000000003E-2</v>
       </c>
-      <c r="D22" s="204">
-        <f>D21*(1-D8)</f>
+      <c r="D22" s="181">
+        <f t="shared" si="4"/>
         <v>3.2947000000000004E-2</v>
       </c>
-      <c r="E22" s="204">
-        <f>E21*(1-E8)</f>
+      <c r="E22" s="181">
+        <f t="shared" si="4"/>
         <v>2.9885000000000002E-2</v>
       </c>
-      <c r="F22" s="204">
-        <f>F21*(1-F8)</f>
+      <c r="F22" s="181">
+        <f t="shared" si="4"/>
         <v>2.65185E-2</v>
       </c>
-      <c r="G22" s="204">
-        <f>G21*(1-G8)</f>
+      <c r="G22" s="181">
+        <f t="shared" si="4"/>
         <v>2.6486000000000003E-2</v>
       </c>
-      <c r="H22" s="204">
-        <f>H21*(1-H8)</f>
+      <c r="H22" s="181">
+        <f t="shared" si="4"/>
         <v>2.5826400000000003E-2</v>
       </c>
-      <c r="I22" s="204">
-        <f>I21*(1-I8)</f>
+      <c r="I22" s="181">
+        <f t="shared" si="4"/>
         <v>3.2453000000000003E-2</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="205" t="s">
+      <c r="A23" s="182" t="s">
         <v>337</v>
       </c>
-      <c r="B23" s="204">
-        <f>IF((B11+B12)=0,0,B11/(B11+B12))</f>
+      <c r="B23" s="181">
+        <f t="shared" ref="B23:I23" si="5">IF((B11+B12)=0,0,B11/(B11+B12))</f>
         <v>0.57794119256316823</v>
       </c>
-      <c r="C23" s="204">
-        <f>IF((C11+C12)=0,0,C11/(C11+C12))</f>
+      <c r="C23" s="181">
+        <f t="shared" si="5"/>
         <v>0.62835191147582903</v>
       </c>
-      <c r="D23" s="204">
-        <f>IF((D11+D12)=0,0,D11/(D11+D12))</f>
+      <c r="D23" s="181">
+        <f t="shared" si="5"/>
         <v>0.78759138163776932</v>
       </c>
-      <c r="E23" s="204">
-        <f>IF((E11+E12)=0,0,E11/(E11+E12))</f>
+      <c r="E23" s="181">
+        <f t="shared" si="5"/>
         <v>0.89823580558918892</v>
       </c>
-      <c r="F23" s="204">
-        <f>IF((F11+F12)=0,0,F11/(F11+F12))</f>
+      <c r="F23" s="181">
+        <f t="shared" si="5"/>
         <v>0.86005615950554537</v>
       </c>
-      <c r="G23" s="204">
-        <f>IF((G11+G12)=0,0,G11/(G11+G12))</f>
+      <c r="G23" s="181">
+        <f t="shared" si="5"/>
         <v>0.83128985173235004</v>
       </c>
-      <c r="H23" s="204">
-        <f>IF((H11+H12)=0,0,H11/(H11+H12))</f>
+      <c r="H23" s="181">
+        <f t="shared" si="5"/>
         <v>0.8295164673204467</v>
       </c>
-      <c r="I23" s="204">
-        <f>IF((I11+I12)=0,0,I11/(I11+I12))</f>
+      <c r="I23" s="181">
+        <f t="shared" si="5"/>
         <v>0.82122667874148336</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="205" t="s">
+      <c r="A24" s="182" t="s">
         <v>336</v>
       </c>
-      <c r="B24" s="204">
-        <f>1-B23</f>
+      <c r="B24" s="181">
+        <f t="shared" ref="B24:I24" si="6">1-B23</f>
         <v>0.42205880743683177</v>
       </c>
-      <c r="C24" s="204">
-        <f>1-C23</f>
+      <c r="C24" s="181">
+        <f t="shared" si="6"/>
         <v>0.37164808852417097</v>
       </c>
-      <c r="D24" s="204">
-        <f>1-D23</f>
+      <c r="D24" s="181">
+        <f t="shared" si="6"/>
         <v>0.21240861836223068</v>
       </c>
-      <c r="E24" s="204">
-        <f>1-E23</f>
+      <c r="E24" s="181">
+        <f t="shared" si="6"/>
         <v>0.10176419441081108</v>
       </c>
-      <c r="F24" s="204">
-        <f>1-F23</f>
+      <c r="F24" s="181">
+        <f t="shared" si="6"/>
         <v>0.13994384049445463</v>
       </c>
-      <c r="G24" s="204">
-        <f>1-G23</f>
+      <c r="G24" s="181">
+        <f t="shared" si="6"/>
         <v>0.16871014826764996</v>
       </c>
-      <c r="H24" s="204">
-        <f>1-H23</f>
+      <c r="H24" s="181">
+        <f t="shared" si="6"/>
         <v>0.1704835326795533</v>
       </c>
-      <c r="I24" s="204">
-        <f>1-I23</f>
+      <c r="I24" s="181">
+        <f t="shared" si="6"/>
         <v>0.17877332125851664</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="207" t="s">
+      <c r="A25" s="184" t="s">
         <v>335</v>
       </c>
-      <c r="B25" s="206">
-        <f>B23*B22+B24*B20</f>
+      <c r="B25" s="183">
+        <f t="shared" ref="B25:I25" si="7">B23*B22+B24*B20</f>
         <v>4.1198113062604638E-2</v>
       </c>
-      <c r="C25" s="206">
-        <f>C23*C22+C24*C20</f>
+      <c r="C25" s="183">
+        <f t="shared" si="7"/>
         <v>3.8899883567933238E-2</v>
       </c>
-      <c r="D25" s="206">
-        <f>D23*D22+D24*D20</f>
+      <c r="D25" s="183">
+        <f t="shared" si="7"/>
         <v>3.6446007170281028E-2</v>
       </c>
-      <c r="E25" s="206">
-        <f>E23*E22+E24*E20</f>
+      <c r="E25" s="183">
+        <f t="shared" si="7"/>
         <v>3.217622083715941E-2</v>
       </c>
-      <c r="F25" s="206">
-        <f>F23*F22+F24*F20</f>
+      <c r="F25" s="183">
+        <f t="shared" si="7"/>
         <v>2.9979521091188604E-2</v>
       </c>
-      <c r="G25" s="206">
-        <f>G23*G22+G24*G20</f>
+      <c r="G25" s="183">
+        <f t="shared" si="7"/>
         <v>3.115151044019359E-2</v>
       </c>
-      <c r="H25" s="206">
-        <f>H23*H22+H24*H20</f>
+      <c r="H25" s="183">
+        <f t="shared" si="7"/>
         <v>3.0438593299699564E-2</v>
       </c>
-      <c r="I25" s="206">
-        <f>I23*I22+I24*I20</f>
+      <c r="I25" s="183">
+        <f t="shared" si="7"/>
         <v>3.7324036684330805E-2</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="208" t="s">
+      <c r="A26" s="243" t="s">
         <v>334</v>
       </c>
-      <c r="B26" s="208"/>
-      <c r="C26" s="208"/>
-      <c r="D26" s="208"/>
-      <c r="E26" s="208"/>
-      <c r="F26" s="208"/>
-      <c r="G26" s="208"/>
-      <c r="H26" s="208"/>
-      <c r="I26" s="208"/>
+      <c r="B26" s="243"/>
+      <c r="C26" s="243"/>
+      <c r="D26" s="243"/>
+      <c r="E26" s="243"/>
+      <c r="F26" s="243"/>
+      <c r="G26" s="243"/>
+      <c r="H26" s="243"/>
+      <c r="I26" s="243"/>
     </row>
     <row r="27" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="207" t="s">
+      <c r="A27" s="184" t="s">
         <v>333</v>
       </c>
-      <c r="B27" s="206">
-        <f>IF(B15=0,0,B9/B15)</f>
+      <c r="B27" s="183">
+        <f t="shared" ref="B27:I27" si="8">IF(B15=0,0,B9/B15)</f>
         <v>0.11556495190571552</v>
       </c>
-      <c r="C27" s="206">
-        <f>IF(C15=0,0,C9/C15)</f>
+      <c r="C27" s="183">
+        <f t="shared" si="8"/>
         <v>0.10577490192541825</v>
       </c>
-      <c r="D27" s="206">
-        <f>IF(D15=0,0,D9/D15)</f>
+      <c r="D27" s="183">
+        <f t="shared" si="8"/>
         <v>0.11421835444619344</v>
       </c>
-      <c r="E27" s="206">
-        <f>IF(E15=0,0,E9/E15)</f>
+      <c r="E27" s="183">
+        <f t="shared" si="8"/>
         <v>0.108414150231297</v>
       </c>
-      <c r="F27" s="206">
-        <f>IF(F15=0,0,F9/F15)</f>
+      <c r="F27" s="183">
+        <f t="shared" si="8"/>
         <v>0.16862971107909305</v>
       </c>
-      <c r="G27" s="206">
-        <f>IF(G15=0,0,G9/G15)</f>
+      <c r="G27" s="183">
+        <f t="shared" si="8"/>
         <v>0.1529155489319424</v>
       </c>
-      <c r="H27" s="206">
-        <f>IF(H15=0,0,H9/H15)</f>
+      <c r="H27" s="183">
+        <f t="shared" si="8"/>
         <v>0.12589163207985316</v>
       </c>
-      <c r="I27" s="206">
-        <f>IF(I15=0,0,I9/I15)</f>
+      <c r="I27" s="183">
+        <f t="shared" si="8"/>
         <v>0.16618977657725273</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="205" t="s">
+      <c r="A28" s="182" t="s">
         <v>332</v>
       </c>
-      <c r="B28" s="204">
-        <f>B25</f>
+      <c r="B28" s="181">
+        <f t="shared" ref="B28:I28" si="9">B25</f>
         <v>4.1198113062604638E-2</v>
       </c>
-      <c r="C28" s="204">
-        <f>C25</f>
+      <c r="C28" s="181">
+        <f t="shared" si="9"/>
         <v>3.8899883567933238E-2</v>
       </c>
-      <c r="D28" s="204">
-        <f>D25</f>
+      <c r="D28" s="181">
+        <f t="shared" si="9"/>
         <v>3.6446007170281028E-2</v>
       </c>
-      <c r="E28" s="204">
-        <f>E25</f>
+      <c r="E28" s="181">
+        <f t="shared" si="9"/>
         <v>3.217622083715941E-2</v>
       </c>
-      <c r="F28" s="204">
-        <f>F25</f>
+      <c r="F28" s="181">
+        <f t="shared" si="9"/>
         <v>2.9979521091188604E-2</v>
       </c>
-      <c r="G28" s="204">
-        <f>G25</f>
+      <c r="G28" s="181">
+        <f t="shared" si="9"/>
         <v>3.115151044019359E-2</v>
       </c>
-      <c r="H28" s="204">
-        <f>H25</f>
+      <c r="H28" s="181">
+        <f t="shared" si="9"/>
         <v>3.0438593299699564E-2</v>
       </c>
-      <c r="I28" s="204">
-        <f>I25</f>
+      <c r="I28" s="181">
+        <f t="shared" si="9"/>
         <v>3.7324036684330805E-2</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="198" t="s">
+      <c r="A29" s="175" t="s">
         <v>331</v>
       </c>
-      <c r="B29" s="202">
-        <f>B27-B28</f>
+      <c r="B29" s="179">
+        <f t="shared" ref="B29:I29" si="10">B27-B28</f>
         <v>7.4366838843110877E-2</v>
       </c>
-      <c r="C29" s="202">
-        <f>C27-C28</f>
+      <c r="C29" s="179">
+        <f t="shared" si="10"/>
         <v>6.6875018357485008E-2</v>
       </c>
-      <c r="D29" s="202">
-        <f>D27-D28</f>
+      <c r="D29" s="179">
+        <f t="shared" si="10"/>
         <v>7.777234727591241E-2</v>
       </c>
-      <c r="E29" s="203">
-        <f>E27-E28</f>
+      <c r="E29" s="180">
+        <f t="shared" si="10"/>
         <v>7.6237929394137594E-2</v>
       </c>
-      <c r="F29" s="203">
-        <f>F27-F28</f>
+      <c r="F29" s="180">
+        <f t="shared" si="10"/>
         <v>0.13865018998790446</v>
       </c>
-      <c r="G29" s="202">
-        <f>G27-G28</f>
+      <c r="G29" s="179">
+        <f t="shared" si="10"/>
         <v>0.1217640384917488</v>
       </c>
-      <c r="H29" s="202">
-        <f>H27-H28</f>
+      <c r="H29" s="179">
+        <f t="shared" si="10"/>
         <v>9.5453038780153598E-2</v>
       </c>
-      <c r="I29" s="202">
-        <f>I27-I28</f>
+      <c r="I29" s="179">
+        <f t="shared" si="10"/>
         <v>0.12886573989292194</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="28" x14ac:dyDescent="0.2">
-      <c r="A30" s="201" t="s">
+      <c r="A30" s="178" t="s">
         <v>330</v>
       </c>
-      <c r="B30" s="199" t="s">
+      <c r="B30" s="176" t="s">
         <v>327</v>
       </c>
-      <c r="C30" s="199" t="s">
+      <c r="C30" s="176" t="s">
         <v>328</v>
       </c>
-      <c r="D30" s="199" t="s">
+      <c r="D30" s="176" t="s">
         <v>328</v>
       </c>
-      <c r="E30" s="200" t="s">
+      <c r="E30" s="177" t="s">
         <v>329</v>
       </c>
-      <c r="F30" s="200" t="s">
+      <c r="F30" s="177" t="s">
         <v>329</v>
       </c>
-      <c r="G30" s="199" t="s">
+      <c r="G30" s="176" t="s">
         <v>328</v>
       </c>
-      <c r="H30" s="199" t="s">
+      <c r="H30" s="176" t="s">
         <v>328</v>
       </c>
-      <c r="I30" s="199" t="s">
+      <c r="I30" s="176" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="198" t="s">
+      <c r="A31" s="175" t="s">
         <v>326</v>
       </c>
-      <c r="B31" s="196">
-        <f>B29*B15</f>
+      <c r="B31" s="173">
+        <f t="shared" ref="B31:I31" si="11">B29*B15</f>
         <v>6795.8648340000009</v>
       </c>
-      <c r="C31" s="196">
-        <f>C29*C15</f>
+      <c r="C31" s="173">
+        <f t="shared" si="11"/>
         <v>5932.3491284557804</v>
       </c>
-      <c r="D31" s="196">
-        <f>D29*D15</f>
+      <c r="D31" s="173">
+        <f t="shared" si="11"/>
         <v>7781.706637559606</v>
       </c>
-      <c r="E31" s="197">
-        <f>E29*E15</f>
+      <c r="E31" s="174">
+        <f t="shared" si="11"/>
         <v>9039.569407227591</v>
       </c>
-      <c r="F31" s="197">
-        <f>F29*F15</f>
+      <c r="F31" s="174">
+        <f t="shared" si="11"/>
         <v>17369.610526019715</v>
       </c>
-      <c r="G31" s="196">
-        <f>G29*G15</f>
+      <c r="G31" s="173">
+        <f t="shared" si="11"/>
         <v>15687.104606968982</v>
       </c>
-      <c r="H31" s="196">
-        <f>H29*H15</f>
+      <c r="H31" s="173">
+        <f t="shared" si="11"/>
         <v>12948.109257489055</v>
       </c>
-      <c r="I31" s="196">
-        <f>I29*I15</f>
+      <c r="I31" s="173">
+        <f t="shared" si="11"/>
         <v>18200.288340906882</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="195" t="s">
+      <c r="A33" s="244" t="s">
         <v>325</v>
       </c>
-      <c r="B33" s="195"/>
-      <c r="C33" s="195"/>
-      <c r="D33" s="195"/>
-      <c r="E33" s="195"/>
-      <c r="F33" s="195"/>
-      <c r="G33" s="195"/>
-      <c r="H33" s="195"/>
-      <c r="I33" s="195"/>
+      <c r="B33" s="244"/>
+      <c r="C33" s="244"/>
+      <c r="D33" s="244"/>
+      <c r="E33" s="244"/>
+      <c r="F33" s="244"/>
+      <c r="G33" s="244"/>
+      <c r="H33" s="244"/>
+      <c r="I33" s="244"/>
     </row>
     <row r="34" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="193" t="s">
+      <c r="A34" s="238" t="s">
         <v>324</v>
       </c>
-      <c r="B34" s="193"/>
-      <c r="C34" s="193"/>
-      <c r="D34" s="193"/>
-      <c r="E34" s="193"/>
-      <c r="F34" s="193"/>
-      <c r="G34" s="193"/>
-      <c r="H34" s="193"/>
-      <c r="I34" s="193"/>
+      <c r="B34" s="238"/>
+      <c r="C34" s="238"/>
+      <c r="D34" s="238"/>
+      <c r="E34" s="238"/>
+      <c r="F34" s="238"/>
+      <c r="G34" s="238"/>
+      <c r="H34" s="238"/>
+      <c r="I34" s="238"/>
     </row>
     <row r="35" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="194" t="s">
+      <c r="A35" s="237" t="s">
         <v>323</v>
       </c>
-      <c r="B35" s="194"/>
-      <c r="C35" s="194"/>
-      <c r="D35" s="194"/>
-      <c r="E35" s="194"/>
-      <c r="F35" s="194"/>
-      <c r="G35" s="194"/>
-      <c r="H35" s="194"/>
-      <c r="I35" s="194"/>
+      <c r="B35" s="237"/>
+      <c r="C35" s="237"/>
+      <c r="D35" s="237"/>
+      <c r="E35" s="237"/>
+      <c r="F35" s="237"/>
+      <c r="G35" s="237"/>
+      <c r="H35" s="237"/>
+      <c r="I35" s="237"/>
     </row>
     <row r="36" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="193" t="s">
+      <c r="A36" s="238" t="s">
         <v>322</v>
       </c>
-      <c r="B36" s="193"/>
-      <c r="C36" s="193"/>
-      <c r="D36" s="193"/>
-      <c r="E36" s="193"/>
-      <c r="F36" s="193"/>
-      <c r="G36" s="193"/>
-      <c r="H36" s="193"/>
-      <c r="I36" s="193"/>
+      <c r="B36" s="238"/>
+      <c r="C36" s="238"/>
+      <c r="D36" s="238"/>
+      <c r="E36" s="238"/>
+      <c r="F36" s="238"/>
+      <c r="G36" s="238"/>
+      <c r="H36" s="238"/>
+      <c r="I36" s="238"/>
     </row>
     <row r="37" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="194" t="s">
+      <c r="A37" s="237" t="s">
         <v>321</v>
       </c>
-      <c r="B37" s="194"/>
-      <c r="C37" s="194"/>
-      <c r="D37" s="194"/>
-      <c r="E37" s="194"/>
-      <c r="F37" s="194"/>
-      <c r="G37" s="194"/>
-      <c r="H37" s="194"/>
-      <c r="I37" s="194"/>
+      <c r="B37" s="237"/>
+      <c r="C37" s="237"/>
+      <c r="D37" s="237"/>
+      <c r="E37" s="237"/>
+      <c r="F37" s="237"/>
+      <c r="G37" s="237"/>
+      <c r="H37" s="237"/>
+      <c r="I37" s="237"/>
     </row>
     <row r="38" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="193" t="s">
+      <c r="A38" s="238" t="s">
         <v>320</v>
       </c>
-      <c r="B38" s="193"/>
-      <c r="C38" s="193"/>
-      <c r="D38" s="193"/>
-      <c r="E38" s="193"/>
-      <c r="F38" s="193"/>
-      <c r="G38" s="193"/>
-      <c r="H38" s="193"/>
-      <c r="I38" s="193"/>
+      <c r="B38" s="238"/>
+      <c r="C38" s="238"/>
+      <c r="D38" s="238"/>
+      <c r="E38" s="238"/>
+      <c r="F38" s="238"/>
+      <c r="G38" s="238"/>
+      <c r="H38" s="238"/>
+      <c r="I38" s="238"/>
     </row>
     <row r="39" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="194" t="s">
+      <c r="A39" s="237" t="s">
         <v>319</v>
       </c>
-      <c r="B39" s="194"/>
-      <c r="C39" s="194"/>
-      <c r="D39" s="194"/>
-      <c r="E39" s="194"/>
-      <c r="F39" s="194"/>
-      <c r="G39" s="194"/>
-      <c r="H39" s="194"/>
-      <c r="I39" s="194"/>
+      <c r="B39" s="237"/>
+      <c r="C39" s="237"/>
+      <c r="D39" s="237"/>
+      <c r="E39" s="237"/>
+      <c r="F39" s="237"/>
+      <c r="G39" s="237"/>
+      <c r="H39" s="237"/>
+      <c r="I39" s="237"/>
     </row>
     <row r="40" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="193" t="s">
+      <c r="A40" s="238" t="s">
         <v>318</v>
       </c>
-      <c r="B40" s="193"/>
-      <c r="C40" s="193"/>
-      <c r="D40" s="193"/>
-      <c r="E40" s="193"/>
-      <c r="F40" s="193"/>
-      <c r="G40" s="193"/>
-      <c r="H40" s="193"/>
-      <c r="I40" s="193"/>
+      <c r="B40" s="238"/>
+      <c r="C40" s="238"/>
+      <c r="D40" s="238"/>
+      <c r="E40" s="238"/>
+      <c r="F40" s="238"/>
+      <c r="G40" s="238"/>
+      <c r="H40" s="238"/>
+      <c r="I40" s="238"/>
     </row>
     <row r="41" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="194" t="s">
+      <c r="A41" s="237" t="s">
         <v>317</v>
       </c>
-      <c r="B41" s="194"/>
-      <c r="C41" s="194"/>
-      <c r="D41" s="194"/>
-      <c r="E41" s="194"/>
-      <c r="F41" s="194"/>
-      <c r="G41" s="194"/>
-      <c r="H41" s="194"/>
-      <c r="I41" s="194"/>
+      <c r="B41" s="237"/>
+      <c r="C41" s="237"/>
+      <c r="D41" s="237"/>
+      <c r="E41" s="237"/>
+      <c r="F41" s="237"/>
+      <c r="G41" s="237"/>
+      <c r="H41" s="237"/>
+      <c r="I41" s="237"/>
     </row>
     <row r="42" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="193" t="s">
+      <c r="A42" s="238" t="s">
         <v>316</v>
       </c>
-      <c r="B42" s="193"/>
-      <c r="C42" s="193"/>
-      <c r="D42" s="193"/>
-      <c r="E42" s="193"/>
-      <c r="F42" s="193"/>
-      <c r="G42" s="193"/>
-      <c r="H42" s="193"/>
-      <c r="I42" s="193"/>
+      <c r="B42" s="238"/>
+      <c r="C42" s="238"/>
+      <c r="D42" s="238"/>
+      <c r="E42" s="238"/>
+      <c r="F42" s="238"/>
+      <c r="G42" s="238"/>
+      <c r="H42" s="238"/>
+      <c r="I42" s="238"/>
     </row>
     <row r="43" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="194" t="s">
+      <c r="A43" s="237" t="s">
         <v>315</v>
       </c>
-      <c r="B43" s="194"/>
-      <c r="C43" s="194"/>
-      <c r="D43" s="194"/>
-      <c r="E43" s="194"/>
-      <c r="F43" s="194"/>
-      <c r="G43" s="194"/>
-      <c r="H43" s="194"/>
-      <c r="I43" s="194"/>
+      <c r="B43" s="237"/>
+      <c r="C43" s="237"/>
+      <c r="D43" s="237"/>
+      <c r="E43" s="237"/>
+      <c r="F43" s="237"/>
+      <c r="G43" s="237"/>
+      <c r="H43" s="237"/>
+      <c r="I43" s="237"/>
     </row>
     <row r="44" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="193" t="s">
+      <c r="A44" s="238" t="s">
         <v>314</v>
       </c>
-      <c r="B44" s="193"/>
-      <c r="C44" s="193"/>
-      <c r="D44" s="193"/>
-      <c r="E44" s="193"/>
-      <c r="F44" s="193"/>
-      <c r="G44" s="193"/>
-      <c r="H44" s="193"/>
-      <c r="I44" s="193"/>
+      <c r="B44" s="238"/>
+      <c r="C44" s="238"/>
+      <c r="D44" s="238"/>
+      <c r="E44" s="238"/>
+      <c r="F44" s="238"/>
+      <c r="G44" s="238"/>
+      <c r="H44" s="238"/>
+      <c r="I44" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A35:I35"/>
     <mergeCell ref="A43:I43"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="A37:I37"/>
@@ -9605,18 +9639,6 @@
     <mergeCell ref="A40:I40"/>
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A33:I33"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A36:I36"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A10:I10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9625,382 +9647,385 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B441A61-8229-E043-B83E-854DEADF0EC5}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" style="3" customWidth="1"/>
     <col min="2" max="4" width="18" style="3" customWidth="1"/>
-    <col min="5" max="5" width="46.6640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="47.1640625" style="3" customWidth="1"/>
     <col min="6" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="222" t="s">
-        <v>446</v>
-      </c>
-      <c r="B1" s="222"/>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
-    </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="221" t="s">
+    <row r="1" spans="1:7" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="239" t="s">
         <v>445</v>
       </c>
-      <c r="B2" s="221"/>
-      <c r="C2" s="221"/>
-      <c r="D2" s="221"/>
-      <c r="E2" s="221"/>
-    </row>
-    <row r="4" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="216" t="s">
+      <c r="B1" s="239"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+    </row>
+    <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="240" t="s">
+        <v>444</v>
+      </c>
+      <c r="B2" s="240"/>
+      <c r="C2" s="240"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+    </row>
+    <row r="4" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="192" t="s">
         <v>224</v>
       </c>
-      <c r="B4" s="216" t="s">
+      <c r="B4" s="192" t="s">
         <v>225</v>
       </c>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="192" t="s">
         <v>226</v>
       </c>
-      <c r="D4" s="216" t="s">
-        <v>444</v>
-      </c>
-      <c r="E4" s="216" t="s">
+      <c r="D4" s="192" t="s">
+        <v>443</v>
+      </c>
+      <c r="E4" s="192" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="210" t="s">
-        <v>443</v>
-      </c>
-      <c r="B5" s="214">
-        <v>59761</v>
-      </c>
-      <c r="C5" s="242">
+    <row r="5" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="186" t="s">
+        <v>442</v>
+      </c>
+      <c r="B5" s="190">
+        <v>58893</v>
+      </c>
+      <c r="C5" s="212">
         <f>B5/B$12</f>
-        <v>0.45523866112101408</v>
-      </c>
-      <c r="D5" s="238" t="s">
+        <v>0.45302307692307692</v>
+      </c>
+      <c r="D5" s="209" t="s">
         <v>429</v>
       </c>
-      <c r="E5" s="240" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="212" t="s">
+      <c r="E5" s="210" t="s">
         <v>441</v>
       </c>
-      <c r="B6" s="214">
-        <v>61342</v>
-      </c>
-      <c r="C6" s="242">
+    </row>
+    <row r="6" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="188" t="s">
+        <v>440</v>
+      </c>
+      <c r="B6" s="190">
+        <v>60895</v>
+      </c>
+      <c r="C6" s="212">
         <f>B6/B$12</f>
-        <v>0.46728217316452608</v>
-      </c>
-      <c r="D6" s="230" t="s">
+        <v>0.46842307692307694</v>
+      </c>
+      <c r="D6" s="202" t="s">
+        <v>435</v>
+      </c>
+      <c r="E6" s="208" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="186" t="s">
+        <v>438</v>
+      </c>
+      <c r="B7" s="190">
+        <v>5000</v>
+      </c>
+      <c r="C7" s="212">
+        <f>B7/B$12</f>
+        <v>3.8461538461538464E-2</v>
+      </c>
+      <c r="D7" s="209" t="s">
+        <v>429</v>
+      </c>
+      <c r="E7" s="210" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="188" t="s">
         <v>436</v>
       </c>
-      <c r="E6" s="237" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="210" t="s">
-        <v>439</v>
-      </c>
-      <c r="B7" s="214">
-        <v>5000</v>
-      </c>
-      <c r="C7" s="242">
-        <f>B7/B$12</f>
-        <v>3.8088273382391027E-2</v>
-      </c>
-      <c r="D7" s="238" t="s">
+      <c r="B8" s="190">
+        <v>1712</v>
+      </c>
+      <c r="C8" s="212">
+        <f>B8/B$12</f>
+        <v>1.316923076923077E-2</v>
+      </c>
+      <c r="D8" s="202" t="s">
+        <v>435</v>
+      </c>
+      <c r="E8" s="208" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="186" t="s">
+        <v>433</v>
+      </c>
+      <c r="B9" s="190">
+        <v>3500</v>
+      </c>
+      <c r="C9" s="212">
+        <f>B9/B$12</f>
+        <v>2.6923076923076925E-2</v>
+      </c>
+      <c r="D9" s="211" t="s">
+        <v>432</v>
+      </c>
+      <c r="E9" s="210" t="s">
+        <v>431</v>
+      </c>
+      <c r="G9" s="216"/>
+    </row>
+    <row r="10" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="188" t="s">
+        <v>430</v>
+      </c>
+      <c r="B10" s="190"/>
+      <c r="C10" s="215">
+        <f>B10/B12</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="209" t="s">
         <v>429</v>
       </c>
-      <c r="E7" s="240" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="212" t="s">
-        <v>437</v>
-      </c>
-      <c r="B8" s="214">
-        <v>1671</v>
-      </c>
-      <c r="C8" s="242">
-        <f>B8/B$12</f>
-        <v>1.2729100964395081E-2</v>
-      </c>
-      <c r="D8" s="230" t="s">
-        <v>436</v>
-      </c>
-      <c r="E8" s="237" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="210" t="s">
-        <v>434</v>
-      </c>
-      <c r="B9" s="214">
-        <v>3500</v>
-      </c>
-      <c r="C9" s="242">
-        <f>B9/B$12</f>
-        <v>2.6661791367673722E-2</v>
-      </c>
-      <c r="D9" s="241" t="s">
-        <v>433</v>
-      </c>
-      <c r="E9" s="240" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="212" t="s">
-        <v>431</v>
-      </c>
-      <c r="B10" s="239"/>
-      <c r="C10" s="238" t="s">
-        <v>430</v>
-      </c>
-      <c r="D10" s="238" t="s">
-        <v>429</v>
-      </c>
-      <c r="E10" s="237" t="s">
+      <c r="E10" s="208" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="236" t="s">
+    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="207" t="s">
         <v>235</v>
       </c>
-      <c r="B12" s="235">
-        <v>131274</v>
-      </c>
-      <c r="C12" s="234">
+      <c r="B12" s="206">
+        <f>SUM(B5:B10)</f>
+        <v>130000</v>
+      </c>
+      <c r="C12" s="205">
         <f>B12/B12</f>
         <v>1</v>
       </c>
-      <c r="D12" s="233"/>
-      <c r="E12" s="232" t="s">
+      <c r="D12" s="204"/>
+      <c r="E12" s="203" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="231" t="s">
+    <row r="15" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="245" t="s">
         <v>426</v>
       </c>
-      <c r="B15" s="231"/>
-      <c r="C15" s="231"/>
-      <c r="D15" s="231"/>
-      <c r="E15" s="231"/>
-    </row>
-    <row r="16" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="216" t="s">
+      <c r="B15" s="245"/>
+      <c r="C15" s="245"/>
+      <c r="D15" s="245"/>
+      <c r="E15" s="245"/>
+    </row>
+    <row r="16" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="192" t="s">
         <v>363</v>
       </c>
-      <c r="B16" s="216" t="s">
+      <c r="B16" s="192" t="s">
         <v>425</v>
       </c>
-      <c r="C16" s="216" t="s">
+      <c r="C16" s="192" t="s">
         <v>424</v>
       </c>
-      <c r="D16" s="216" t="s">
+      <c r="D16" s="192" t="s">
         <v>241</v>
       </c>
-      <c r="E16" s="216" t="s">
+      <c r="E16" s="192" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="226" t="s">
+    <row r="17" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="198" t="s">
         <v>422</v>
       </c>
-      <c r="B17" s="225" t="s">
+      <c r="B17" s="197" t="s">
         <v>421</v>
       </c>
-      <c r="C17" s="225" t="s">
+      <c r="C17" s="197" t="s">
         <v>420</v>
       </c>
-      <c r="D17" s="230" t="s">
+      <c r="D17" s="202" t="s">
         <v>419</v>
       </c>
-      <c r="E17" s="223" t="s">
+      <c r="E17" s="195" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="229" t="s">
+      <c r="A18" s="201" t="s">
         <v>417</v>
       </c>
-      <c r="B18" s="228" t="s">
+      <c r="B18" s="200" t="s">
         <v>416</v>
       </c>
-      <c r="C18" s="228" t="s">
+      <c r="C18" s="200" t="s">
         <v>415</v>
       </c>
-      <c r="D18" s="224" t="s">
+      <c r="D18" s="196" t="s">
         <v>414</v>
       </c>
-      <c r="E18" s="227" t="s">
+      <c r="E18" s="199" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="226" t="s">
+    <row r="19" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="198" t="s">
         <v>412</v>
       </c>
-      <c r="B19" s="225" t="s">
+      <c r="B19" s="197" t="s">
         <v>411</v>
       </c>
-      <c r="C19" s="225" t="s">
+      <c r="C19" s="197" t="s">
         <v>410</v>
       </c>
-      <c r="D19" s="230" t="s">
+      <c r="D19" s="202" t="s">
         <v>409</v>
       </c>
-      <c r="E19" s="223" t="s">
+      <c r="E19" s="195" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="229" t="s">
+      <c r="A20" s="201" t="s">
         <v>407</v>
       </c>
-      <c r="B20" s="228" t="s">
+      <c r="B20" s="200" t="s">
         <v>406</v>
       </c>
-      <c r="C20" s="228" t="s">
+      <c r="C20" s="200" t="s">
         <v>405</v>
       </c>
-      <c r="D20" s="230" t="s">
+      <c r="D20" s="202" t="s">
         <v>404</v>
       </c>
-      <c r="E20" s="227" t="s">
+      <c r="E20" s="199" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="226" t="s">
+      <c r="A21" s="198" t="s">
         <v>402</v>
       </c>
-      <c r="B21" s="225" t="s">
+      <c r="B21" s="197" t="s">
         <v>401</v>
       </c>
-      <c r="C21" s="225" t="s">
+      <c r="C21" s="197" t="s">
         <v>400</v>
       </c>
-      <c r="D21" s="230" t="s">
+      <c r="D21" s="202" t="s">
         <v>399</v>
       </c>
-      <c r="E21" s="223" t="s">
+      <c r="E21" s="195" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="229" t="s">
+      <c r="A22" s="201" t="s">
         <v>397</v>
       </c>
-      <c r="B22" s="228" t="s">
+      <c r="B22" s="200" t="s">
         <v>396</v>
       </c>
-      <c r="C22" s="228" t="s">
+      <c r="C22" s="200" t="s">
         <v>395</v>
       </c>
-      <c r="D22" s="224" t="s">
+      <c r="D22" s="196" t="s">
         <v>394</v>
       </c>
-      <c r="E22" s="227" t="s">
+      <c r="E22" s="199" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="226" t="s">
+      <c r="A23" s="198" t="s">
         <v>332</v>
       </c>
-      <c r="B23" s="225" t="s">
+      <c r="B23" s="197" t="s">
         <v>392</v>
       </c>
-      <c r="C23" s="225" t="s">
+      <c r="C23" s="197" t="s">
         <v>391</v>
       </c>
-      <c r="D23" s="224" t="s">
+      <c r="D23" s="196" t="s">
         <v>390</v>
       </c>
-      <c r="E23" s="223" t="s">
+      <c r="E23" s="195" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="229" t="s">
+      <c r="A24" s="201" t="s">
         <v>388</v>
       </c>
-      <c r="B24" s="228" t="s">
+      <c r="B24" s="200" t="s">
         <v>387</v>
       </c>
-      <c r="C24" s="228" t="s">
+      <c r="C24" s="200" t="s">
         <v>386</v>
       </c>
-      <c r="D24" s="230" t="s">
+      <c r="D24" s="202" t="s">
         <v>385</v>
       </c>
-      <c r="E24" s="227" t="s">
+      <c r="E24" s="199" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="226" t="s">
+      <c r="A25" s="198" t="s">
         <v>383</v>
       </c>
-      <c r="B25" s="225" t="s">
+      <c r="B25" s="197" t="s">
         <v>382</v>
       </c>
-      <c r="C25" s="225" t="s">
+      <c r="C25" s="197" t="s">
         <v>381</v>
       </c>
-      <c r="D25" s="230" t="s">
+      <c r="D25" s="202" t="s">
         <v>380</v>
       </c>
-      <c r="E25" s="223" t="s">
+      <c r="E25" s="195" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="229" t="s">
+      <c r="A26" s="201" t="s">
         <v>378</v>
       </c>
-      <c r="B26" s="228" t="s">
+      <c r="B26" s="200" t="s">
         <v>377</v>
       </c>
-      <c r="C26" s="228" t="s">
+      <c r="C26" s="200" t="s">
         <v>376</v>
       </c>
-      <c r="D26" s="224" t="s">
+      <c r="D26" s="196" t="s">
         <v>375</v>
       </c>
-      <c r="E26" s="227" t="s">
+      <c r="E26" s="199" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="226" t="s">
+      <c r="A27" s="198" t="s">
         <v>373</v>
       </c>
-      <c r="B27" s="225" t="s">
+      <c r="B27" s="197" t="s">
         <v>372</v>
       </c>
-      <c r="C27" s="225" t="s">
+      <c r="C27" s="197" t="s">
         <v>371</v>
       </c>
-      <c r="D27" s="224" t="s">
+      <c r="D27" s="196" t="s">
         <v>370</v>
       </c>
-      <c r="E27" s="223" t="s">
+      <c r="E27" s="195" t="s">
         <v>369</v>
       </c>
     </row>
@@ -10024,87 +10049,87 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="219" t="s">
         <v>312</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
-      <c r="L1" s="143"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="143"/>
-      <c r="O1" s="143"/>
-      <c r="P1" s="143"/>
-      <c r="Q1" s="143"/>
-      <c r="R1" s="143"/>
-      <c r="S1" s="143"/>
-      <c r="T1" s="143"/>
-      <c r="U1" s="143"/>
-      <c r="V1" s="143"/>
-      <c r="W1" s="143"/>
-      <c r="X1" s="143"/>
-      <c r="Y1" s="143"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="219"/>
+      <c r="K1" s="219"/>
+      <c r="L1" s="219"/>
+      <c r="M1" s="219"/>
+      <c r="N1" s="219"/>
+      <c r="O1" s="219"/>
+      <c r="P1" s="219"/>
+      <c r="Q1" s="219"/>
+      <c r="R1" s="219"/>
+      <c r="S1" s="219"/>
+      <c r="T1" s="219"/>
+      <c r="U1" s="219"/>
+      <c r="V1" s="219"/>
+      <c r="W1" s="219"/>
+      <c r="X1" s="219"/>
+      <c r="Y1" s="219"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="143"/>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="143"/>
-      <c r="K2" s="143"/>
-      <c r="L2" s="143"/>
-      <c r="M2" s="143"/>
-      <c r="N2" s="143"/>
-      <c r="O2" s="143"/>
-      <c r="P2" s="143"/>
-      <c r="Q2" s="143"/>
-      <c r="R2" s="143"/>
-      <c r="S2" s="143"/>
-      <c r="T2" s="143"/>
-      <c r="U2" s="143"/>
-      <c r="V2" s="143"/>
-      <c r="W2" s="143"/>
-      <c r="X2" s="143"/>
-      <c r="Y2" s="143"/>
+      <c r="A2" s="219"/>
+      <c r="B2" s="219"/>
+      <c r="C2" s="219"/>
+      <c r="D2" s="219"/>
+      <c r="E2" s="219"/>
+      <c r="F2" s="219"/>
+      <c r="G2" s="219"/>
+      <c r="H2" s="219"/>
+      <c r="I2" s="219"/>
+      <c r="J2" s="219"/>
+      <c r="K2" s="219"/>
+      <c r="L2" s="219"/>
+      <c r="M2" s="219"/>
+      <c r="N2" s="219"/>
+      <c r="O2" s="219"/>
+      <c r="P2" s="219"/>
+      <c r="Q2" s="219"/>
+      <c r="R2" s="219"/>
+      <c r="S2" s="219"/>
+      <c r="T2" s="219"/>
+      <c r="U2" s="219"/>
+      <c r="V2" s="219"/>
+      <c r="W2" s="219"/>
+      <c r="X2" s="219"/>
+      <c r="Y2" s="219"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="143"/>
-      <c r="B3" s="143"/>
-      <c r="C3" s="143"/>
-      <c r="D3" s="143"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="143"/>
-      <c r="G3" s="143"/>
-      <c r="H3" s="143"/>
-      <c r="I3" s="143"/>
-      <c r="J3" s="143"/>
-      <c r="K3" s="143"/>
-      <c r="L3" s="143"/>
-      <c r="M3" s="143"/>
-      <c r="N3" s="143"/>
-      <c r="O3" s="143"/>
-      <c r="P3" s="143"/>
-      <c r="Q3" s="143"/>
-      <c r="R3" s="143"/>
-      <c r="S3" s="143"/>
-      <c r="T3" s="143"/>
-      <c r="U3" s="143"/>
-      <c r="V3" s="143"/>
-      <c r="W3" s="143"/>
-      <c r="X3" s="143"/>
-      <c r="Y3" s="143"/>
+      <c r="A3" s="219"/>
+      <c r="B3" s="219"/>
+      <c r="C3" s="219"/>
+      <c r="D3" s="219"/>
+      <c r="E3" s="219"/>
+      <c r="F3" s="219"/>
+      <c r="G3" s="219"/>
+      <c r="H3" s="219"/>
+      <c r="I3" s="219"/>
+      <c r="J3" s="219"/>
+      <c r="K3" s="219"/>
+      <c r="L3" s="219"/>
+      <c r="M3" s="219"/>
+      <c r="N3" s="219"/>
+      <c r="O3" s="219"/>
+      <c r="P3" s="219"/>
+      <c r="Q3" s="219"/>
+      <c r="R3" s="219"/>
+      <c r="S3" s="219"/>
+      <c r="T3" s="219"/>
+      <c r="U3" s="219"/>
+      <c r="V3" s="219"/>
+      <c r="W3" s="219"/>
+      <c r="X3" s="219"/>
+      <c r="Y3" s="219"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10144,10 +10169,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="135" t="s">
+      <c r="A1" s="222" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="135"/>
+      <c r="B1" s="222"/>
       <c r="C1" s="61"/>
       <c r="D1" s="61"/>
       <c r="E1" s="61"/>
@@ -10160,32 +10185,32 @@
       <c r="L1" s="61"/>
     </row>
     <row r="2" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="135"/>
-      <c r="B2" s="135"/>
-      <c r="C2" s="133" t="s">
+      <c r="A2" s="222"/>
+      <c r="B2" s="222"/>
+      <c r="C2" s="220" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="134"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
-      <c r="L2" s="133" t="s">
+      <c r="D2" s="221"/>
+      <c r="E2" s="221"/>
+      <c r="F2" s="221"/>
+      <c r="G2" s="221"/>
+      <c r="H2" s="221"/>
+      <c r="L2" s="220" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="134"/>
-      <c r="N2" s="134"/>
-      <c r="O2" s="134"/>
-      <c r="P2" s="134"/>
-      <c r="Q2" s="134"/>
-      <c r="S2" s="133" t="s">
+      <c r="M2" s="221"/>
+      <c r="N2" s="221"/>
+      <c r="O2" s="221"/>
+      <c r="P2" s="221"/>
+      <c r="Q2" s="221"/>
+      <c r="S2" s="220" t="s">
         <v>20</v>
       </c>
-      <c r="T2" s="134"/>
-      <c r="V2" s="133" t="s">
+      <c r="T2" s="221"/>
+      <c r="V2" s="220" t="s">
         <v>21</v>
       </c>
-      <c r="W2" s="134"/>
+      <c r="W2" s="221"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="G3" s="66" t="s">
@@ -13036,7 +13061,7 @@
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C47">
         <v>0.31</v>
@@ -13068,10 +13093,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C30:C32">
-    <cfRule type="cellIs" dxfId="23" priority="35" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="36" operator="greaterThan">
       <formula>$C$29</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="36" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="35" operator="lessThan">
       <formula>$C$29</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13084,10 +13109,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:D32">
-    <cfRule type="cellIs" dxfId="19" priority="33" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="34" operator="greaterThan">
       <formula>$D$29</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="34" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="33" operator="lessThan">
       <formula>$D$29</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13100,10 +13125,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30:E32">
-    <cfRule type="cellIs" dxfId="15" priority="31" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="32" operator="greaterThan">
       <formula>$E$29</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="32" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="31" operator="lessThan">
       <formula>$E$29</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13132,34 +13157,34 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H30:H32 H46">
-    <cfRule type="cellIs" dxfId="7" priority="25" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="26" operator="greaterThan">
       <formula>$H$29</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="26" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="25" operator="lessThan">
       <formula>$H$29</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30:I32 I46">
-    <cfRule type="cellIs" dxfId="5" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="24" operator="lessThan">
       <formula>$I$29</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="24" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="21" operator="greaterThan">
       <formula>$I$29</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J30:J32 J46">
-    <cfRule type="cellIs" dxfId="3" priority="20" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="23" operator="lessThan">
       <formula>$J$29</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="23" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="20" operator="greaterThan">
       <formula>$J$29</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30:K32 K46">
-    <cfRule type="cellIs" dxfId="1" priority="19" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="22" operator="lessThan">
       <formula>$K$29</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="22" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="19" operator="greaterThan">
       <formula>$K$29</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13204,26 +13229,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="223" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
+      <c r="B1" s="224"/>
+      <c r="C1" s="224"/>
+      <c r="D1" s="224"/>
+      <c r="E1" s="224"/>
+      <c r="F1" s="224"/>
+      <c r="G1" s="224"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="225" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
-      <c r="G2" s="137"/>
+      <c r="B2" s="224"/>
+      <c r="C2" s="224"/>
+      <c r="D2" s="224"/>
+      <c r="E2" s="224"/>
+      <c r="F2" s="224"/>
+      <c r="G2" s="224"/>
     </row>
     <row r="3" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -13606,15 +13631,15 @@
     </row>
     <row r="28" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="139" t="s">
+      <c r="A29" s="226" t="s">
         <v>183</v>
       </c>
-      <c r="B29" s="137"/>
-      <c r="C29" s="137"/>
-      <c r="D29" s="137"/>
-      <c r="E29" s="137"/>
-      <c r="F29" s="137"/>
-      <c r="G29" s="137"/>
+      <c r="B29" s="224"/>
+      <c r="C29" s="224"/>
+      <c r="D29" s="224"/>
+      <c r="E29" s="224"/>
+      <c r="F29" s="224"/>
+      <c r="G29" s="224"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -13639,22 +13664,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="223" t="s">
         <v>184</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
+      <c r="B1" s="224"/>
+      <c r="C1" s="224"/>
+      <c r="D1" s="224"/>
+      <c r="E1" s="224"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="225" t="s">
         <v>185</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
+      <c r="B2" s="224"/>
+      <c r="C2" s="224"/>
+      <c r="D2" s="224"/>
+      <c r="E2" s="224"/>
     </row>
     <row r="3" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -13994,37 +14019,37 @@
     </row>
     <row r="33" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="141" t="s">
+      <c r="A35" s="228" t="s">
         <v>211</v>
       </c>
-      <c r="B35" s="137"/>
-      <c r="C35" s="137"/>
-      <c r="D35" s="137"/>
-      <c r="E35" s="137"/>
-      <c r="F35" s="137"/>
-      <c r="G35" s="137"/>
+      <c r="B35" s="224"/>
+      <c r="C35" s="224"/>
+      <c r="D35" s="224"/>
+      <c r="E35" s="224"/>
+      <c r="F35" s="224"/>
+      <c r="G35" s="224"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="138" t="s">
+      <c r="A36" s="225" t="s">
         <v>212</v>
       </c>
-      <c r="B36" s="137"/>
-      <c r="C36" s="137"/>
-      <c r="D36" s="137"/>
-      <c r="E36" s="137"/>
-      <c r="F36" s="137"/>
-      <c r="G36" s="137"/>
+      <c r="B36" s="224"/>
+      <c r="C36" s="224"/>
+      <c r="D36" s="224"/>
+      <c r="E36" s="224"/>
+      <c r="F36" s="224"/>
+      <c r="G36" s="224"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="140" t="s">
+      <c r="A38" s="227" t="s">
         <v>213</v>
       </c>
-      <c r="B38" s="137"/>
-      <c r="C38" s="137"/>
-      <c r="D38" s="137"/>
-      <c r="E38" s="137"/>
-      <c r="F38" s="137"/>
-      <c r="G38" s="137"/>
+      <c r="B38" s="224"/>
+      <c r="C38" s="224"/>
+      <c r="D38" s="224"/>
+      <c r="E38" s="224"/>
+      <c r="F38" s="224"/>
+      <c r="G38" s="224"/>
     </row>
     <row r="39" spans="1:7" ht="26" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
@@ -14211,15 +14236,15 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="140" t="s">
+      <c r="A48" s="227" t="s">
         <v>221</v>
       </c>
-      <c r="B48" s="137"/>
-      <c r="C48" s="137"/>
-      <c r="D48" s="137"/>
-      <c r="E48" s="137"/>
-      <c r="F48" s="137"/>
-      <c r="G48" s="137"/>
+      <c r="B48" s="224"/>
+      <c r="C48" s="224"/>
+      <c r="D48" s="224"/>
+      <c r="E48" s="224"/>
+      <c r="F48" s="224"/>
+      <c r="G48" s="224"/>
     </row>
     <row r="49" spans="1:7" ht="26" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -14432,20 +14457,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="228" t="s">
         <v>222</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
+      <c r="B1" s="224"/>
+      <c r="C1" s="224"/>
+      <c r="D1" s="224"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="225" t="s">
         <v>223</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="B2" s="224"/>
+      <c r="C2" s="224"/>
+      <c r="D2" s="224"/>
     </row>
     <row r="3" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -14594,23 +14619,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="1fd0f161-8cac-428d-bb0d-db3eea82b135" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AADB740074F67C41A4C35EB618A06C22" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f9ff74c96d282be4d376c4880d01f28f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="39c253dd-750e-49f2-b9e0-df4649350370" xmlns:ns4="1fd0f161-8cac-428d-bb0d-db3eea82b135" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ed4c3aca728f71d233ae273cdfab16d" ns3:_="" ns4:_="">
     <xsd:import namespace="39c253dd-750e-49f2-b9e0-df4649350370"/>
@@ -14805,10 +14813,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="1fd0f161-8cac-428d-bb0d-db3eea82b135" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9C11964-986B-4414-95FD-16130A9F1BE3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23BE8E31-9C1B-4B34-88DF-333714514273}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="39c253dd-750e-49f2-b9e0-df4649350370"/>
+    <ds:schemaRef ds:uri="1fd0f161-8cac-428d-bb0d-db3eea82b135"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -14831,20 +14867,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23BE8E31-9C1B-4B34-88DF-333714514273}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9C11964-986B-4414-95FD-16130A9F1BE3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="39c253dd-750e-49f2-b9e0-df4649350370"/>
-    <ds:schemaRef ds:uri="1fd0f161-8cac-428d-bb0d-db3eea82b135"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
